--- a/Luban/Config/Datas/#BattleBuffConfig.xlsx
+++ b/Luban/Config/Datas/#BattleBuffConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3A10656-9A89-43D1-B864-5BB0EBD9A0E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6513F88-8CE3-4E67-B760-4B58EE76ED75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="55">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -83,10 +83,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>UnderHitMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>AfterClashMoment</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -99,14 +95,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>息开始扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>被作为目标时扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>释放成功后扳机</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -115,10 +103,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>命中后扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>交锋后扳机</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -127,14 +111,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>AsTargetActionMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>StartActionWheelMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>战斗开始扳机</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -147,14 +123,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CalculateActionWheelMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计算息的时候调用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>RoundEndMoment</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -168,6 +136,114 @@
   </si>
   <si>
     <t>ReleaseSkillActionMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(list#sep=,),int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff层数减少扳机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffLevelReduceMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BeforeActionMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BeforeUnderActionMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动前</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到行动前调用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到行动后调用扳机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AfterUnderActionMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckSkillRelease</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断技能能否释放</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckSkillReleaseRelation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断技能能否释放或与（0或，1与）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OverlayType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff叠加类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff减少时扳机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffReduceMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffAddMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加buff层数时扳机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Limit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>限制层数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Script</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff脚本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleBuffBase</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -175,7 +251,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -190,6 +266,13 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -214,8 +297,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -532,261 +618,362 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:P5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:W5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="8" width="41.25" customWidth="1"/>
-    <col min="9" max="9" width="24.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.75" customWidth="1"/>
-    <col min="13" max="13" width="16.375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="29.625" style="1" customWidth="1"/>
+    <col min="6" max="7" width="38.375" style="1" customWidth="1"/>
+    <col min="8" max="9" width="42.875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="38.375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="26" style="1" customWidth="1"/>
+    <col min="12" max="14" width="41.25" style="1" customWidth="1"/>
+    <col min="15" max="15" width="24.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.75" style="1" customWidth="1"/>
+    <col min="18" max="18" width="17.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="27.5" style="1" customWidth="1"/>
+    <col min="21" max="21" width="18.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="26" style="1" customWidth="1"/>
+    <col min="24" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" t="s">
+      <c r="O1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="W1" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1">
+        <v>5</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I1" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" t="s">
-        <v>15</v>
-      </c>
-      <c r="O1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P1" t="s">
-        <v>32</v>
+      <c r="K4" s="1">
+        <v>1</v>
+      </c>
+      <c r="L4" s="1">
+        <v>1</v>
+      </c>
+      <c r="M4" s="1">
+        <v>1</v>
+      </c>
+      <c r="N4" s="1">
+        <v>1</v>
+      </c>
+      <c r="O4" s="1">
+        <v>1</v>
+      </c>
+      <c r="P4" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>1</v>
+      </c>
+      <c r="R4" s="1">
+        <v>1</v>
+      </c>
+      <c r="S4" s="1">
+        <v>1</v>
+      </c>
+      <c r="T4" s="1">
+        <v>1</v>
+      </c>
+      <c r="U4" s="1">
+        <v>1</v>
+      </c>
+      <c r="V4" s="1">
+        <v>1</v>
+      </c>
+      <c r="W4" s="1">
+        <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J2" t="s">
-        <v>5</v>
-      </c>
-      <c r="K2" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" t="s">
-        <v>5</v>
-      </c>
-      <c r="M2" t="s">
-        <v>5</v>
-      </c>
-      <c r="N2" t="s">
-        <v>5</v>
-      </c>
-      <c r="O2" t="s">
-        <v>5</v>
-      </c>
-      <c r="P2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" t="s">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" s="1">
+        <v>2</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O3" t="s">
-        <v>34</v>
-      </c>
-      <c r="P3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-      <c r="N4">
-        <v>1</v>
-      </c>
-      <c r="O4">
-        <v>1</v>
-      </c>
-      <c r="P4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-      <c r="N5">
-        <v>1</v>
-      </c>
-      <c r="O5">
-        <v>1</v>
-      </c>
-      <c r="P5">
+      <c r="K5" s="1">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1">
+        <v>1</v>
+      </c>
+      <c r="M5" s="1">
+        <v>1</v>
+      </c>
+      <c r="N5" s="1">
+        <v>1</v>
+      </c>
+      <c r="O5" s="1">
+        <v>1</v>
+      </c>
+      <c r="P5" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>1</v>
+      </c>
+      <c r="R5" s="1">
+        <v>1</v>
+      </c>
+      <c r="S5" s="1">
+        <v>1</v>
+      </c>
+      <c r="T5" s="1">
+        <v>1</v>
+      </c>
+      <c r="U5" s="1">
+        <v>1</v>
+      </c>
+      <c r="V5" s="1">
+        <v>1</v>
+      </c>
+      <c r="W5" s="1">
         <v>1</v>
       </c>
     </row>

--- a/Luban/Config/Datas/#BattleBuffConfig.xlsx
+++ b/Luban/Config/Datas/#BattleBuffConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6513F88-8CE3-4E67-B760-4B58EE76ED75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83FAFF1-E0FA-4EF7-8220-A47A48FA2F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="4995" yWindow="4455" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -301,8 +301,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">

--- a/Luban/Config/Datas/#BattleBuffConfig.xlsx
+++ b/Luban/Config/Datas/#BattleBuffConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83FAFF1-E0FA-4EF7-8220-A47A48FA2F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83396745-BC1C-4286-B0DE-DEADAF10868B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4995" yWindow="4455" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="3975" yWindow="3780" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="66">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -67,14 +67,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>buff1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>buff2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>DoDesitionMoment</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -147,14 +139,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>BuffLevelReduceMoment</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -244,6 +228,65 @@
   </si>
   <si>
     <t>BattleBuffBase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>快速防守1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>快速防守2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加时破翻倍，结束时清楚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加时防翻倍，结束时清除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>999999</t>
+  </si>
+  <si>
+    <t>999999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>破招buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001005</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -618,25 +661,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:W9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="4" width="9" style="1"/>
+    <col min="1" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="10.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.75" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="29.625" style="1" customWidth="1"/>
     <col min="6" max="7" width="38.375" style="1" customWidth="1"/>
     <col min="8" max="9" width="42.875" style="1" customWidth="1"/>
     <col min="10" max="10" width="38.375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="26" style="1" customWidth="1"/>
-    <col min="12" max="14" width="41.25" style="1" customWidth="1"/>
-    <col min="15" max="15" width="24.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="22.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.75" style="1" customWidth="1"/>
-    <col min="18" max="18" width="17.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="22.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="27.5" style="1" customWidth="1"/>
-    <col min="21" max="21" width="18.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="26" style="1" customWidth="1"/>
+    <col min="11" max="12" width="26" style="1" customWidth="1"/>
+    <col min="13" max="15" width="41.25" style="1" customWidth="1"/>
+    <col min="16" max="16" width="24.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.75" style="1" customWidth="1"/>
+    <col min="19" max="19" width="17.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="22.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="27.5" style="1" customWidth="1"/>
+    <col min="22" max="22" width="18.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.75" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -645,7 +689,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -654,61 +698,61 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="L1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.2">
@@ -734,52 +778,52 @@
         <v>5</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.2">
@@ -796,61 +840,61 @@
         <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="L3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="R3" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="S3" s="1" t="s">
         <v>17</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.2">
@@ -858,61 +902,28 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F4" s="1">
-        <v>1</v>
-      </c>
-      <c r="G4" s="1">
-        <v>5</v>
+      <c r="G4" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K4" s="1">
-        <v>1</v>
-      </c>
-      <c r="L4" s="1">
-        <v>1</v>
-      </c>
-      <c r="M4" s="1">
-        <v>1</v>
-      </c>
-      <c r="N4" s="1">
-        <v>1</v>
-      </c>
-      <c r="O4" s="1">
-        <v>1</v>
-      </c>
-      <c r="P4" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="1">
-        <v>1</v>
-      </c>
-      <c r="R4" s="1">
-        <v>1</v>
-      </c>
-      <c r="S4" s="1">
-        <v>1</v>
-      </c>
-      <c r="T4" s="1">
-        <v>1</v>
-      </c>
-      <c r="U4" s="1">
-        <v>1</v>
-      </c>
-      <c r="V4" s="1">
-        <v>1</v>
-      </c>
-      <c r="W4" s="1">
-        <v>1</v>
+        <v>58</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.2">
@@ -920,61 +931,54 @@
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F5" s="1">
-        <v>2</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1</v>
+      <c r="G5" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K5" s="1">
-        <v>1</v>
-      </c>
-      <c r="L5" s="1">
-        <v>1</v>
-      </c>
-      <c r="M5" s="1">
-        <v>1</v>
-      </c>
-      <c r="N5" s="1">
-        <v>1</v>
-      </c>
-      <c r="O5" s="1">
-        <v>1</v>
-      </c>
-      <c r="P5" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>1</v>
-      </c>
-      <c r="R5" s="1">
-        <v>1</v>
-      </c>
-      <c r="S5" s="1">
-        <v>1</v>
-      </c>
-      <c r="T5" s="1">
-        <v>1</v>
-      </c>
-      <c r="U5" s="1">
-        <v>1</v>
-      </c>
-      <c r="V5" s="1">
-        <v>1</v>
-      </c>
-      <c r="W5" s="1">
-        <v>1</v>
+        <v>58</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Config/Datas/#BattleBuffConfig.xlsx
+++ b/Luban/Config/Datas/#BattleBuffConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83396745-BC1C-4286-B0DE-DEADAF10868B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6512203D-0EFA-47C4-B7D7-FFA80340F25F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3975" yWindow="3780" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,8 +24,67 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Admin</author>
+  </authors>
+  <commentList>
+    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{173F07C8-62C6-4A91-90E1-273164FD34EA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+战斗开始 = 1,
+回合开始 = 2,
+决定后 = 3,
+行动前 = 4,
+受到行动前 = 5,
+交锋前 = 6,
+交锋后 = 7,
+释放成功 = 8,
+受到行动后 = 9,
+行动后 = 10,
+回合结束 = 11,
+buff添加 = 12,
+buff结束 = 13,
+技能结束 = 14,
+buff减少 = 15,
+息开始 = 16,
+计算息 = 17,
+直到下次行动前 = 18
+减少一层 = 1,
+清空 = 2,
+减少最后一次叠加后总计数的1/4 = 3,
+减少最后一次叠加后总计数的1/3 = 4,
+减少最后一次叠加后总计数的1/2 = 5,
+上次行动前获取的全部清空 = 6</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="339">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -231,15 +290,98 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>快速防守1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>快速防守2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>添加时破翻倍，结束时清楚</t>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加时防翻倍，结束时清除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>999999</t>
+  </si>
+  <si>
+    <t>999999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>破招buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>破防翻倍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加时破翻倍，结束时清除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000201</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000202</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>息开始的扳机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActionWheelStartMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受击回血</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000301</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到直接伤害时回血30%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>盾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>护体</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleBuffShield</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -247,46 +389,2128 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>添加时防翻倍，结束时清除</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>999999</t>
-  </si>
-  <si>
-    <t>999999</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>破招buff</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1001002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1001003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1001004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1001005</t>
+    <t>-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>延迟护体</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>延迟盾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>800001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ParamEx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>额外参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>##参数备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleBuffShieldDelay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(回合开始添加盾)延迟盾的触发扳机,触发后清空层数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(list#sep=,),float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回避</t>
+  </si>
+  <si>
+    <t>反击</t>
+  </si>
+  <si>
+    <t>迅速</t>
+  </si>
+  <si>
+    <t>刚聚</t>
+  </si>
+  <si>
+    <t>玄聚</t>
+  </si>
+  <si>
+    <t>力增</t>
+  </si>
+  <si>
+    <t>技增</t>
+  </si>
+  <si>
+    <t>武增</t>
+  </si>
+  <si>
+    <t>术增</t>
+  </si>
+  <si>
+    <t>巧增</t>
+  </si>
+  <si>
+    <t>藏身</t>
+  </si>
+  <si>
+    <t>隐魂</t>
+  </si>
+  <si>
+    <t>雷行</t>
+  </si>
+  <si>
+    <t>行字诀</t>
+  </si>
+  <si>
+    <t>匿形</t>
+  </si>
+  <si>
+    <t>避殃</t>
+  </si>
+  <si>
+    <t>借法</t>
+  </si>
+  <si>
+    <t>岳环架势</t>
+  </si>
+  <si>
+    <t>御守架势</t>
+  </si>
+  <si>
+    <t>龙腾</t>
+  </si>
+  <si>
+    <t>回春</t>
+  </si>
+  <si>
+    <t>缓速</t>
+  </si>
+  <si>
+    <t>失衡</t>
+  </si>
+  <si>
+    <t>封穴↑</t>
+  </si>
+  <si>
+    <t>封穴↓</t>
+  </si>
+  <si>
+    <t>封穴←</t>
+  </si>
+  <si>
+    <t>封穴→</t>
+  </si>
+  <si>
+    <t>破绽</t>
+  </si>
+  <si>
+    <t>伤口</t>
+  </si>
+  <si>
+    <t>刚屏</t>
+  </si>
+  <si>
+    <t>玄屏</t>
+  </si>
+  <si>
+    <t>力衰</t>
+  </si>
+  <si>
+    <t>技衰</t>
+  </si>
+  <si>
+    <t>武衰</t>
+  </si>
+  <si>
+    <t>术衰</t>
+  </si>
+  <si>
+    <t>僵硬</t>
+  </si>
+  <si>
+    <t>过劲</t>
+  </si>
+  <si>
+    <t>盲目</t>
+  </si>
+  <si>
+    <t>武式禁</t>
+  </si>
+  <si>
+    <t>术式禁</t>
+  </si>
+  <si>
+    <t>技式禁</t>
+  </si>
+  <si>
+    <t>法式禁</t>
+  </si>
+  <si>
+    <t>妖毒</t>
+  </si>
+  <si>
+    <t>妖毒侵蚀</t>
+  </si>
+  <si>
+    <t>毒向↑</t>
+  </si>
+  <si>
+    <t>毒向→</t>
+  </si>
+  <si>
+    <t>毒向↓</t>
+  </si>
+  <si>
+    <t>毒向←</t>
+  </si>
+  <si>
+    <t>失持</t>
+  </si>
+  <si>
+    <t>共生</t>
+  </si>
+  <si>
+    <t>赤沸</t>
+  </si>
+  <si>
+    <t>寒沁</t>
+  </si>
+  <si>
+    <t>晕眩</t>
+  </si>
+  <si>
+    <t>苦印</t>
+  </si>
+  <si>
+    <t>毒瘴</t>
+  </si>
+  <si>
+    <t>昏沉</t>
+  </si>
+  <si>
+    <t>交鸣</t>
+  </si>
+  <si>
+    <t>先发制人</t>
+  </si>
+  <si>
+    <t>猊煞</t>
+  </si>
+  <si>
+    <t>异鳞</t>
+  </si>
+  <si>
+    <t>饕餮万物</t>
+  </si>
+  <si>
+    <t>破招</t>
+  </si>
+  <si>
+    <t>敷宵剑</t>
+  </si>
+  <si>
+    <t>断筋式</t>
+  </si>
+  <si>
+    <t>傍剑</t>
+  </si>
+  <si>
+    <t>御敌式</t>
+  </si>
+  <si>
+    <t>留劲·武杀式↑</t>
+  </si>
+  <si>
+    <t>留劲·武杀式→</t>
+  </si>
+  <si>
+    <t>留劲·武杀式↓</t>
+  </si>
+  <si>
+    <t>留劲·武杀式←</t>
+  </si>
+  <si>
+    <t>留劲·术杀式↑</t>
+  </si>
+  <si>
+    <t>留劲·术杀式→</t>
+  </si>
+  <si>
+    <t>留劲·术杀式↓</t>
+  </si>
+  <si>
+    <t>留劲·术杀式←</t>
+  </si>
+  <si>
+    <t>留劲·技杀式↑</t>
+  </si>
+  <si>
+    <t>留劲·技御式→</t>
+  </si>
+  <si>
+    <t>留劲·技御式↓</t>
+  </si>
+  <si>
+    <t>留劲·技御式←</t>
+  </si>
+  <si>
+    <t>留劲·法咒式↑</t>
+  </si>
+  <si>
+    <t>留劲·法咒式→</t>
+  </si>
+  <si>
+    <t>留劲·法咒式↓</t>
+  </si>
+  <si>
+    <t>留劲·法咒式←</t>
+  </si>
+  <si>
+    <t>死楔</t>
+  </si>
+  <si>
+    <t>燃息</t>
+  </si>
+  <si>
+    <t>平</t>
+  </si>
+  <si>
+    <t>彻</t>
+  </si>
+  <si>
+    <t>起</t>
+  </si>
+  <si>
+    <t>固灾</t>
+  </si>
+  <si>
+    <t>玉摄念</t>
+  </si>
+  <si>
+    <t>戴面</t>
+  </si>
+  <si>
+    <t>巧来方计</t>
+  </si>
+  <si>
+    <t>残缺</t>
+  </si>
+  <si>
+    <t>兽化身</t>
+  </si>
+  <si>
+    <t>禽化身</t>
+  </si>
+  <si>
+    <t>祖化身</t>
+  </si>
+  <si>
+    <t>烈命</t>
+  </si>
+  <si>
+    <t>瘴鬼本源</t>
+  </si>
+  <si>
+    <t>药力·刚炁恢复</t>
+  </si>
+  <si>
+    <t>药力·玄炁恢复</t>
+  </si>
+  <si>
+    <t>药力·稳势</t>
+  </si>
+  <si>
+    <t>药力·体恢复</t>
+  </si>
+  <si>
+    <t>药力·速</t>
+  </si>
+  <si>
+    <t>药力·力</t>
+  </si>
+  <si>
+    <t>药力·技</t>
+  </si>
+  <si>
+    <t>药力·破</t>
+  </si>
+  <si>
+    <t>药力·防</t>
+  </si>
+  <si>
+    <t>药力·巧</t>
+  </si>
+  <si>
+    <t>行动后获得1个随机的键</t>
+  </si>
+  <si>
+    <t>无法成为行动的目标</t>
+  </si>
+  <si>
+    <t>无法被施加异常状态</t>
+  </si>
+  <si>
+    <t>玄炁上限增加10</t>
+  </si>
+  <si>
+    <t>若可以成为行动目标，则其余友方无法成为行动目标</t>
+  </si>
+  <si>
+    <t>全部的破、防的提升效果增加30%</t>
+  </si>
+  <si>
+    <t>回合开始扣除1层异常状态并获得{[int]}层护体，该状态被清除时只会扣除2层</t>
+  </si>
+  <si>
+    <t>行动后扣除1层该状态并恢复30+gr*6体，在下1息转移至包括自身首个行动的友方目标，若没有发生转移或被消除时扣除2层</t>
+  </si>
+  <si>
+    <r>
+      <t>至少减少受到的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>武杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>{[int]}%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>敌手的力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>的直接伤害，至少减少行动目标对自身的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>术杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>伤害{[int]}%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>敌手的技</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>的直接伤害</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>受到攻击后</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>自身未存在行动则消耗一层</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF92D050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>反击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>状态对其使用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>武杀式：反击</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>每层使</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>武杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>威力增加5百分比</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>每层使</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>术杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>威力增加5百分比</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>抵免{[int]}次敌手</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>武杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="0.39997558519241921"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>技御式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>带来的异常状态，防增加30+GR*3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>抵免{[int]}次敌手</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>术杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="7" tint="0.39997558519241921"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>法咒式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>带来的异常状态，破增加30+GR*3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>武杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>直接造成伤害时根据行动加快效果提升伤害共{[int]}%，行动加快{[int]}息</t>
+    </r>
+  </si>
+  <si>
+    <t>每层使行动延迟{[int]}息</t>
+  </si>
+  <si>
+    <t>增益状态无法生效，每层使行动延迟{[int]}息</t>
+  </si>
+  <si>
+    <t>出招时无法使用↑键</t>
+  </si>
+  <si>
+    <t>出招时无法使用↓键</t>
+  </si>
+  <si>
+    <t>出招时无法使用←键</t>
+  </si>
+  <si>
+    <t>出招时无法使用→键</t>
+  </si>
+  <si>
+    <t>行动的意图被揭示</t>
+  </si>
+  <si>
+    <t>每层使扣除键时同时扣除{[int]}的体</t>
+  </si>
+  <si>
+    <t>无法使用4键招式</t>
+  </si>
+  <si>
+    <t>无法使用变式</t>
+  </si>
+  <si>
+    <t>使用招式每消耗1个↑键减少1层妖毒侵蚀状态与妖毒状态</t>
+  </si>
+  <si>
+    <t>使用招式每消耗1个→键减少1层妖毒侵蚀状态与妖毒状态</t>
+  </si>
+  <si>
+    <t>使用招式每消耗1个↓键减少1层妖毒侵蚀状态与妖毒状态</t>
+  </si>
+  <si>
+    <t>使用招式每消耗1个←键减少1层妖毒侵蚀状态与妖毒状态</t>
+  </si>
+  <si>
+    <t>无法获得增益状态</t>
+  </si>
+  <si>
+    <t>施加者受到伤害时扣除伤害量{[int]}%的体</t>
+  </si>
+  <si>
+    <t>每层使玄炁消耗增加{[int]}</t>
+  </si>
+  <si>
+    <t>每层使刚炁消耗增加{[int]}</t>
+  </si>
+  <si>
+    <t>无法使用招式</t>
+  </si>
+  <si>
+    <t>该消除时扣除65+GR*13的体</t>
+  </si>
+  <si>
+    <t>无法使用招式，受到招式的直接攻击或被消除时扣除2层</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>每层使获得的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>刚炁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>减少{[int]}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>每层使获得的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>玄炁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>减少{[int]}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>每层使</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>减少{[int]}%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>每层使</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>技</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>减少{[int]}%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>每层使</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>武杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>威力减少{[int]}的百分比</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>每层使</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>术杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>威力减少{[int]}的百分比</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>减少</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>武杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>{[int]}%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>的直接伤害，减少对非交锋目标的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>术杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>{[int]}%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>技</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>的直接伤害</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>无法使用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>武杀式</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>无法使用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>术杀式</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>无法使用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>技御式</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>无法使用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="7" tint="0.39997558519241921"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>法咒式</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>行动开始</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>在本次行动中随机污染x个键，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>使用招式每消耗1个被污染的键</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>获得1层妖毒侵蚀状态（正常的键优先消耗），因任何原因减少被污染的键时等量减少妖毒状态的层数</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>每次获得该状态</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>扣除</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>层数*2%的当前命</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>回合结束时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>扣除10+GR*2的体上限并恢复等量的体</t>
+    </r>
+  </si>
+  <si>
+    <t>行动加快8息</t>
+  </si>
+  <si>
+    <t>可使用猊煞变派系招式</t>
+  </si>
+  <si>
+    <t>允许消耗体上限21+GR*3：1替代刚炁的消耗，消耗至多不能超过当前已损生命</t>
+  </si>
+  <si>
+    <t>武杀式、术杀式威力提升，越弱的招式越多。技御式、法咒式刚炁或玄炁消耗减少（取最高的一项减少）</t>
+  </si>
+  <si>
+    <t>招式的力或技取值从角色自身属性改为250+GR*25</t>
+  </si>
+  <si>
+    <t>无法直接清除异常状态</t>
+  </si>
+  <si>
+    <t>下一次行动中恢复刚炁时获得等量玄炁，恢复玄炁时获得等量刚炁</t>
+  </si>
+  <si>
+    <t>属性能够与他人交换（该buff所记录的基础属性已覆盖持有者自身基础属性）</t>
+  </si>
+  <si>
+    <t>下一次术杀式的基础伤害不会低于140%技</t>
+  </si>
+  <si>
+    <t>每层使键上限减少1</t>
+  </si>
+  <si>
+    <t>力提升15%，防提升15%，层数大于4效果翻倍并变身为兽</t>
+  </si>
+  <si>
+    <t>巧提升15%，速提升15%，层数大于4效果翻倍并变身为禽</t>
+  </si>
+  <si>
+    <t>技提升15%，破提升15%，层数大于4效果翻倍并变身为祖</t>
+  </si>
+  <si>
+    <t>武杀式行动觉决定后威力提升不会低于该状态*5的百分比，每层使回合结束扣除20+GR*4的体并增加1层烈命状态</t>
+  </si>
+  <si>
+    <t>被击破时随机转移至另一个友方，若是术杀式击破则扣除1层，完全清除时结束战斗</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>回合开始</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>层数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>超过3则清除该状态并</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>刚炁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>+{[int]}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>受到攻击后</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>对攻击者造成其等级挂钩的伤害</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>每20层使</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF92D050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>速</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>-{[int]}，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>+{[int]}，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>技</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>+{[int]}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>若受到</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>的直接攻击所削减体，本次行动失败（消耗行动所需的炁，触发行动后扳机）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>我方杀式命中时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>消耗1层敷宵剑状态</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>对其目标释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>术杀式：敷宵剑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>，三息内至多释放一次</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>敷宵剑交锋后</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>施加2层</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>力衰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>状态</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>{[int]}受到单方面杀式攻击前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>消耗1层敷宵剑状态</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>，对其释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>术杀式：敷宵剑</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>术杀式：敷宵剑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>威力增加效果翻倍，威力增加35%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>下次行动时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>若首个键为↑或→则获得额外回合，且行动是首个键为↑的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>非武杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>或是首个键为→的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>武杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>则获得3个随机的键</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>下次行动时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>若首个键为→或↓则获得额外回合，且行动是首个键为→的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>非武杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>或是首个键为↓的武杀式则获得3个随机的键</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>下次行动时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>若首个键为↓或←则获得额外回合，且行动是首个键为↓的非武杀式或是首个键为←的武杀式则获得3个随机的键</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>下次行动时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>若首个键为←或↑则获得额外回合，且行动是首个键为←的非武杀式或是首个键为↑的武杀式则获得3个随机的键</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>下次行动时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>若首个键为↑或→则获得额外回合，且行动是首个键为↑的非术杀式或是首个键为→的术杀式则获得3个随机的键</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>下次行动时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>若首个键为→或↓则获得额外回合，且行动是首个键为→的非术杀式或是首个键为↓的术杀式则获得3个随机的键</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>下次行动时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>若首个键为↓或←则获得额外回合，且行动是首个键为↓的非术杀式或是首个键为←的术杀式则获得3个随机的键</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>下次行动时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>若首个键为←或↑则获得额外回合，且行动是首个键为←的非术杀式或是首个键为↑的术杀式则获得3个随机的键</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>下次行动时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>若首个键为↑或→则获得额外回合，且行动是首个键为↑的非技御式或是首个键为→的技御式则获得3个随机的键</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>下次行动时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>若首个键为→或↓则获得额外回合，且行动是首个键为→的非技御式或是首个键为↓的技御式则获得3个随机的键</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>下次行动时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>若首个键为↓或←则获得额外回合，且行动是首个键为↓的非技御式或是首个键为←的技御式则获得3个随机的键</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>下次行动时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>若首个键为←或↑则获得额外回合，且行动是首个键为←的非技御式或是首个键为↑的技御式则获得3个随机的键</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>下次行动时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>若首个键为↑或→则获得额外回合，且行动是首个键为↑的非法咒式或是首个键为→的法咒式则获得3个随机的键</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>下次行动时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>若首个键为→或↓则获得额外回合，且行动是首个键为→的非法咒式或是首个键为↓的法咒式则获得3个随机的键</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>下次行动时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>若首个键为↓或←则获得额外回合，且行动是首个键为↓的非法咒式或是首个键为←的法咒式则获得3个随机的键</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>下次行动时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>若首个键为←或↑则获得额外回合，且行动是首个键为←的非法咒式或是首个键为↑的法咒式则获得3个随机的键</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>命</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>低于30%即死</t>
+    </r>
+  </si>
+  <si>
+    <t>行动开始固定增加5刚炁</t>
+  </si>
+  <si>
+    <t>行动开始固定增加5玄炁</t>
+  </si>
+  <si>
+    <t>回合开始固定增加7玄炁</t>
+  </si>
+  <si>
+    <t>回合开始固定增加25玄炁</t>
+  </si>
+  <si>
+    <t>行动开始固定增加9玄炁</t>
+  </si>
+  <si>
+    <t>回合开始固定增加12玄炁</t>
+  </si>
+  <si>
+    <t>行动结束获得1个随机的键</t>
+  </si>
+  <si>
+    <t>回合结束获得1个随机的键</t>
+  </si>
+  <si>
+    <t>回合结束获得4个随机的键</t>
+  </si>
+  <si>
+    <t>回合结束获得4个↑键</t>
+  </si>
+  <si>
+    <t>回合结束获得4个↓键</t>
+  </si>
+  <si>
+    <t>回合结束获得4个←键</t>
+  </si>
+  <si>
+    <t>回合结束获得4个→键</t>
+  </si>
+  <si>
+    <t>回合结束固定恢复35+GR*7体</t>
+  </si>
+  <si>
+    <t>回合结束固定恢复175+GR*25体</t>
+  </si>
+  <si>
+    <t>速提升20+GR*1</t>
+  </si>
+  <si>
+    <t>力提升40+GR*2</t>
+  </si>
+  <si>
+    <t>技提升40+GR*2</t>
+  </si>
+  <si>
+    <t>破提升14+GR*0.7</t>
+  </si>
+  <si>
+    <t>防提升14+GR*0.7</t>
+  </si>
+  <si>
+    <t>巧提升20+GR*1</t>
+  </si>
+  <si>
+    <t>速提升10+GR*0.5</t>
+  </si>
+  <si>
+    <t>巧提升10+GR*0.5</t>
+  </si>
+  <si>
+    <r>
+      <t>回合开始</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>固定增加{[int]}刚炁</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>行动开始</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>固定增加{[int]}刚炁</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>行动决定后</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>揭示目标直到下{[int]}息内的已决定行动</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>心眼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CalculateActionWheelMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算息的时候扳机调用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每层使行动加快1息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>每层使获得的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>刚炁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>增加1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>每层使获得的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>玄炁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>增加1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>每层使</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>增加10%</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>每层使</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>技</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>增加10%</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每层使巧增加10%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11,6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>800002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>810001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>护盾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>810002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>甲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>延迟甲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleBuffArmor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleBuffArmorDelay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(回合开始添加甲)延迟甲的触发扳机,触发后清空层数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -294,7 +2518,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -317,13 +2541,125 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF92D050"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFF00"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="0.39997558519241921"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="7" tint="0.39997558519241921"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -340,11 +2676,35 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -660,31 +3020,41 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:W9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
+  <dimension ref="A1:AB184"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
-    <col min="3" max="3" width="10.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.625" style="1" customWidth="1"/>
-    <col min="6" max="7" width="38.375" style="1" customWidth="1"/>
-    <col min="8" max="9" width="42.875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="38.375" style="1" customWidth="1"/>
-    <col min="11" max="12" width="26" style="1" customWidth="1"/>
-    <col min="13" max="15" width="41.25" style="1" customWidth="1"/>
-    <col min="16" max="16" width="24.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="22.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.75" style="1" customWidth="1"/>
-    <col min="19" max="19" width="17.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="22.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="27.5" style="1" customWidth="1"/>
-    <col min="22" max="22" width="18.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9" style="1"/>
+    <col min="3" max="3" width="13.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="158.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="48.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="34.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="31.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="27.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="22.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="29.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="21.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="28" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="27.5" style="1" customWidth="1"/>
+    <col min="27" max="27" width="21.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -701,61 +3071,76 @@
         <v>48</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="R1" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="T1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -778,22 +3163,19 @@
         <v>5</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="J2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>26</v>
@@ -825,8 +3207,23 @@
       <c r="W2" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -843,146 +3240,2868 @@
         <v>49</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="R3" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="S3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="T3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="U3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="V3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="W3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="X3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="Y3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="Z3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="V3" s="1" t="s">
+      <c r="AA3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="W3" s="1" t="s">
+      <c r="AB3" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B4" s="1">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B6" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z6" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" s="9" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B8" s="2">
+        <v>70101</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B9" s="2">
+        <v>70201</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B10" s="2">
+        <v>70301</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B11" s="2">
+        <v>70401</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B12" s="2">
+        <v>70501</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B13" s="2">
+        <v>70601</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B14" s="2">
+        <v>70701</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B15" s="2">
+        <v>70801</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B16" s="2">
+        <v>70901</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B17" s="2">
+        <v>71001</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B18" s="2">
+        <v>71101</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B19" s="2">
+        <v>71201</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B20" s="2">
+        <v>71301</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B21" s="2">
+        <v>71401</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B22" s="2">
+        <v>71601</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B23" s="2">
+        <v>71701</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B24" s="2">
+        <v>71801</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B25" s="2">
+        <v>71901</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B26" s="2">
+        <v>72001</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B27" s="2">
+        <v>72101</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B28" s="2">
+        <v>72201</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B29" s="2">
+        <v>72301</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B31" s="2">
+        <v>72401</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H31" s="3">
+        <v>10</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B32" s="2">
+        <v>72501</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H32" s="3">
+        <v>8</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B33" s="2">
+        <v>72601</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H33" s="3">
         <v>1</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="I33" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B34" s="2">
+        <v>72701</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="H34" s="3">
+        <v>1</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B35" s="2">
+        <v>72801</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H35" s="3">
+        <v>1</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B36" s="2">
+        <v>72901</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H36" s="3">
+        <v>1</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B37" s="2">
+        <v>73001</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H37" s="3">
+        <v>1</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B38" s="2">
+        <v>73101</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H38" s="3">
+        <v>1</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B39" s="2">
+        <v>73201</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H39" s="3">
+        <v>5</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B40" s="2">
+        <v>73301</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H40" s="3">
+        <v>5</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B41" s="2">
+        <v>73401</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H41" s="3">
+        <v>5</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B42" s="2">
+        <v>73501</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H42" s="3">
+        <v>5</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B43" s="2">
+        <v>73601</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H43" s="3">
+        <v>5</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B44" s="2">
+        <v>73701</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H44" s="3">
+        <v>5</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B45" s="2">
+        <v>73801</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H45" s="3">
+        <v>1</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B46" s="2">
+        <v>73901</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H46" s="3">
+        <v>1</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B47" s="2">
+        <v>74001</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H47" s="3">
+        <v>1</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B48" s="2">
+        <v>74101</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H48" s="3">
+        <v>1</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B49" s="2">
+        <v>74201</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H49" s="3">
+        <v>1</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B50" s="2">
+        <v>74301</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H50" s="3">
+        <v>1</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B51" s="2">
+        <v>74401</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H51" s="3">
+        <v>1</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B52" s="2">
+        <v>74501</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H52" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B53" s="2">
+        <v>74601</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H53" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B54" s="2">
+        <v>74701</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H54" s="3">
+        <v>1</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B55" s="2">
+        <v>74801</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H55" s="3">
+        <v>1</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B56" s="2">
+        <v>74901</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H56" s="3">
+        <v>1</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="57" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B57" s="2">
+        <v>75001</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H57" s="3">
+        <v>1</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B58" s="2">
+        <v>75101</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H58" s="3">
+        <v>1</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B59" s="2">
+        <v>75201</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H59" s="3">
+        <v>-1</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B60" s="2">
+        <v>75301</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H60" s="3">
+        <v>5</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B61" s="2">
+        <v>75401</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H61" s="3">
+        <v>5</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="62" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B62" s="2">
+        <v>75501</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H62" s="3">
+        <v>1</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="63" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B63" s="2">
+        <v>75601</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H63" s="3">
+        <v>1</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B64" s="2">
+        <v>75701</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H64" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B65" s="2">
+        <v>75801</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H65" s="3">
+        <v>-1</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="66" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="67" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B67" s="2">
+        <v>75901</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="68" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B68" s="2">
+        <v>76001</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="69" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B69" s="2">
+        <v>76101</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="70" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B70" s="2">
+        <v>76201</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="71" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B71" s="2">
+        <v>76301</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="72" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B72" s="2">
+        <v>76401</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="73" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B73" s="2">
+        <v>76501</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="74" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B74" s="2">
+        <v>76601</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="75" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B75" s="2">
+        <v>76701</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="76" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B76" s="2">
+        <v>76801</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="77" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B77" s="2">
+        <v>76901</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="78" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B78" s="2">
+        <v>77001</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="79" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B79" s="2">
+        <v>77101</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="80" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B80" s="2">
+        <v>77201</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="81" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B81" s="2">
+        <v>77301</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="82" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B82" s="2">
+        <v>77401</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="83" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B83" s="2">
+        <v>77501</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="84" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B84" s="2">
+        <v>77601</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="85" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B85" s="2">
+        <v>77701</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="86" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B86" s="2">
+        <v>77801</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="87" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B87" s="2">
+        <v>77901</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="88" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B88" s="2">
+        <v>78001</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="89" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B89" s="2">
+        <v>78101</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="90" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B90" s="2">
+        <v>78201</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="91" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B91" s="2">
+        <v>78301</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="92" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B92" s="2">
+        <v>78401</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="93" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B93" s="2">
+        <v>78501</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="94" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B94" s="2">
+        <v>78601</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="95" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B95" s="2">
+        <v>78701</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="96" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B96" s="2">
+        <v>78801</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="97" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B97" s="2">
+        <v>78901</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D97" s="2"/>
+      <c r="E97" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="98" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B98" s="2">
+        <v>79001</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="99" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B99" s="2">
+        <v>79101</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="100" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B100" s="2">
+        <v>79201</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="101" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B101" s="2">
+        <v>79301</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="102" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B102" s="2">
+        <v>79401</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="103" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B103" s="2">
+        <v>79501</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="104" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B104" s="2">
+        <v>79601</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="105" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B105" s="2">
+        <v>79701</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="106" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B106" s="2">
+        <v>79801</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="107" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B107" s="2">
+        <v>79901</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="108" spans="2:5" s="9" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="109" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B109" s="2">
+        <v>80001</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="110" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B110" s="2">
+        <v>80101</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="111" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B111" s="2">
+        <v>80201</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="112" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B112" s="2">
+        <v>80301</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="113" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B113" s="2">
+        <v>80401</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="114" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B114" s="2">
+        <v>80501</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="115" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B115" s="2">
+        <v>80601</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="116" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B116" s="2">
+        <v>80701</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="117" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B117" s="2">
+        <v>80801</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="118" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B118" s="2">
+        <v>80901</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="119" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B119" s="2">
+        <v>81001</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="120" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B120" s="2">
+        <v>81101</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="121" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B121" s="2">
+        <v>81201</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="122" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B122" s="2">
+        <v>81301</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="123" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B123" s="2">
+        <v>81401</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="124" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B124" s="2">
+        <v>81501</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="125" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B125" s="2">
+        <v>81601</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="126" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B126" s="2">
+        <v>81701</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="127" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B127" s="2">
+        <v>81801</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="128" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B128" s="2">
+        <v>81901</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="129" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B129" s="2">
+        <v>82001</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="130" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B130" s="2">
+        <v>82101</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="131" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B131" s="2">
+        <v>82201</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="132" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B132" s="2">
+        <v>82301</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="133" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B133" s="2">
+        <v>82401</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="134" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B134" s="2">
+        <v>82501</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="135" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B135" s="2">
+        <v>82601</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="136" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B136" s="2">
+        <v>82701</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="137" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B137" s="2">
+        <v>82801</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="138" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B138" s="2">
+        <v>82901</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="139" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B139" s="2">
+        <v>83001</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="140" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B140" s="2">
+        <v>83101</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="141" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B141" s="2">
+        <v>83201</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="142" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B142" s="2">
+        <v>83301</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="143" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B143" s="2">
+        <v>83401</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="144" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B144" s="2">
+        <v>83501</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="145" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B145" s="2">
+        <v>83601</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="146" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B146" s="2">
+        <v>83701</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="147" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B147" s="2">
+        <v>83801</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="148" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B148" s="2">
+        <v>83901</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="149" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B149" s="2">
+        <v>84001</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="150" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B150" s="2">
+        <v>84101</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="151" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B151" s="2">
+        <v>84201</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="152" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B152" s="2">
+        <v>84301</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="153" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B153" s="2">
+        <v>84401</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="154" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B154" s="2">
+        <v>84501</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="155" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B155" s="2">
+        <v>84601</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="156" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B156" s="2">
+        <v>84701</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="157" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B157" s="2">
+        <v>84801</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="158" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B158" s="2">
+        <v>84901</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="159" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B159" s="2">
+        <v>85001</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="160" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B160" s="2">
+        <v>85101</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="161" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B161" s="2">
+        <v>85201</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="162" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B162" s="2">
+        <v>85301</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="163" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B163" s="2">
+        <v>85401</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="164" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B164" s="2">
+        <v>85501</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="165" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B165" s="2">
+        <v>85601</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="166" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B166" s="2">
+        <v>85701</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="167" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B167" s="2">
+        <v>85801</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="168" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B168" s="2">
+        <v>85901</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="169" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B169" s="2">
+        <v>86001</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="170" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B170" s="2">
+        <v>86101</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="171" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B171" s="2">
+        <v>86201</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="172" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B172" s="2">
+        <v>86301</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="173" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B173" s="2">
+        <v>86401</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="174" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B174" s="2">
+        <v>86501</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="175" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B175" s="2">
+        <v>86601</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="176" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B176" s="2">
+        <v>86701</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="177" spans="1:26" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A177" s="9" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="178" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B178" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G178" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H178" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I178" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="179" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B179" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G179" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H179" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J179" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K179" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="180" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B180" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="G180" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H180" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I180" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="181" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B181" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="G181" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H181" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J181" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K181" s="1" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="183" spans="1:26" s="9" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="184" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B184" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D184" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F4" s="1" t="s">
+      <c r="E184" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G184" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H184" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I184" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B5" s="1">
-        <v>2</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B9" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F9" s="1" t="s">
+      <c r="Z184" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="U9" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Luban/Config/Datas/#BattleBuffConfig.xlsx
+++ b/Luban/Config/Datas/#BattleBuffConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C997B4-FC6D-45EB-8AD8-9D7A43FB2E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4317A62-AD2A-4D9A-83A4-3F509E059AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="406">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -416,2334 +416,2388 @@
     <t>藏身</t>
   </si>
   <si>
+    <t>雷行</t>
+  </si>
+  <si>
+    <t>行字诀</t>
+  </si>
+  <si>
+    <t>匿形</t>
+  </si>
+  <si>
+    <t>借法</t>
+  </si>
+  <si>
+    <t>岳环架势</t>
+  </si>
+  <si>
+    <t>御守架势</t>
+  </si>
+  <si>
+    <t>龙腾</t>
+  </si>
+  <si>
+    <t>回春</t>
+  </si>
+  <si>
+    <t>缓速</t>
+  </si>
+  <si>
+    <t>失衡</t>
+  </si>
+  <si>
+    <t>封穴↓</t>
+  </si>
+  <si>
+    <t>封穴←</t>
+  </si>
+  <si>
+    <t>封穴→</t>
+  </si>
+  <si>
+    <t>破绽</t>
+  </si>
+  <si>
+    <t>伤口</t>
+  </si>
+  <si>
+    <t>刚屏</t>
+  </si>
+  <si>
+    <t>玄屏</t>
+  </si>
+  <si>
+    <t>力衰</t>
+  </si>
+  <si>
+    <t>技衰</t>
+  </si>
+  <si>
+    <t>武衰</t>
+  </si>
+  <si>
+    <t>术衰</t>
+  </si>
+  <si>
+    <t>僵硬</t>
+  </si>
+  <si>
+    <t>过劲</t>
+  </si>
+  <si>
+    <t>盲目</t>
+  </si>
+  <si>
+    <t>武式禁</t>
+  </si>
+  <si>
+    <t>术式禁</t>
+  </si>
+  <si>
+    <t>法式禁</t>
+  </si>
+  <si>
+    <t>妖毒</t>
+  </si>
+  <si>
+    <t>妖毒侵蚀</t>
+  </si>
+  <si>
+    <t>毒向↑</t>
+  </si>
+  <si>
+    <t>毒向→</t>
+  </si>
+  <si>
+    <t>毒向↓</t>
+  </si>
+  <si>
+    <t>毒向←</t>
+  </si>
+  <si>
+    <t>失持</t>
+  </si>
+  <si>
+    <t>共生</t>
+  </si>
+  <si>
+    <t>晕眩</t>
+  </si>
+  <si>
+    <t>苦印</t>
+  </si>
+  <si>
+    <t>昏沉</t>
+  </si>
+  <si>
+    <t>交鸣</t>
+  </si>
+  <si>
+    <t>先发制人</t>
+  </si>
+  <si>
+    <t>异鳞</t>
+  </si>
+  <si>
+    <t>饕餮万物</t>
+  </si>
+  <si>
+    <t>破招</t>
+  </si>
+  <si>
+    <t>敷宵剑</t>
+  </si>
+  <si>
+    <t>断筋式</t>
+  </si>
+  <si>
+    <t>傍剑</t>
+  </si>
+  <si>
+    <t>御敌式</t>
+  </si>
+  <si>
+    <t>留劲·武杀式↑</t>
+  </si>
+  <si>
+    <t>留劲·武杀式→</t>
+  </si>
+  <si>
+    <t>留劲·武杀式↓</t>
+  </si>
+  <si>
+    <t>留劲·武杀式←</t>
+  </si>
+  <si>
+    <t>留劲·术杀式↑</t>
+  </si>
+  <si>
+    <t>留劲·术杀式→</t>
+  </si>
+  <si>
+    <t>留劲·术杀式↓</t>
+  </si>
+  <si>
+    <t>留劲·术杀式←</t>
+  </si>
+  <si>
+    <t>留劲·技杀式↑</t>
+  </si>
+  <si>
+    <t>留劲·技御式→</t>
+  </si>
+  <si>
+    <t>留劲·技御式↓</t>
+  </si>
+  <si>
+    <t>留劲·技御式←</t>
+  </si>
+  <si>
+    <t>留劲·法咒式↑</t>
+  </si>
+  <si>
+    <t>留劲·法咒式→</t>
+  </si>
+  <si>
+    <t>留劲·法咒式↓</t>
+  </si>
+  <si>
+    <t>留劲·法咒式←</t>
+  </si>
+  <si>
+    <t>死楔</t>
+  </si>
+  <si>
+    <t>燃息</t>
+  </si>
+  <si>
+    <t>平</t>
+  </si>
+  <si>
+    <t>彻</t>
+  </si>
+  <si>
+    <t>起</t>
+  </si>
+  <si>
+    <t>固灾</t>
+  </si>
+  <si>
+    <t>玉摄念</t>
+  </si>
+  <si>
+    <t>戴面</t>
+  </si>
+  <si>
+    <t>巧来方计</t>
+  </si>
+  <si>
+    <t>残缺</t>
+  </si>
+  <si>
+    <t>兽化身</t>
+  </si>
+  <si>
+    <t>禽化身</t>
+  </si>
+  <si>
+    <t>祖化身</t>
+  </si>
+  <si>
+    <t>烈命</t>
+  </si>
+  <si>
+    <t>瘴鬼本源</t>
+  </si>
+  <si>
+    <t>药力·刚炁恢复</t>
+  </si>
+  <si>
+    <t>药力·玄炁恢复</t>
+  </si>
+  <si>
+    <t>药力·稳势</t>
+  </si>
+  <si>
+    <t>药力·体恢复</t>
+  </si>
+  <si>
+    <t>药力·速</t>
+  </si>
+  <si>
+    <t>药力·力</t>
+  </si>
+  <si>
+    <t>药力·技</t>
+  </si>
+  <si>
+    <t>药力·破</t>
+  </si>
+  <si>
+    <t>药力·防</t>
+  </si>
+  <si>
+    <t>药力·巧</t>
+  </si>
+  <si>
+    <t>行动后获得1个随机的键</t>
+  </si>
+  <si>
+    <t>无法成为行动的目标</t>
+  </si>
+  <si>
+    <t>无法被施加异常状态</t>
+  </si>
+  <si>
+    <t>玄炁上限增加10</t>
+  </si>
+  <si>
+    <t>若可以成为行动目标，则其余友方无法成为行动目标</t>
+  </si>
+  <si>
+    <t>全部的破、防的提升效果增加30%</t>
+  </si>
+  <si>
+    <t>回合开始扣除1层异常状态并获得{[int]}层护体，该状态被清除时只会扣除2层</t>
+  </si>
+  <si>
+    <t>行动后扣除1层该状态并恢复30+gr*6体，在下1息转移至包括自身首个行动的友方目标，若没有发生转移或被消除时扣除2层</t>
+  </si>
+  <si>
+    <r>
+      <t>至少减少受到的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>武杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>{[int]}%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>敌手的力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>的直接伤害，至少减少行动目标对自身的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>术杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>伤害{[int]}%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>敌手的技</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>的直接伤害</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>受到攻击后</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>自身未存在行动则消耗一层</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF92D050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>反击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>状态对其使用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>武杀式：反击</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>每层使</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>武杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>威力增加5百分比</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>每层使</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>术杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>威力增加5百分比</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>抵免{[int]}次敌手</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>武杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="0.39997558519241921"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>技御式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>带来的异常状态，防增加30+GR*3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>抵免{[int]}次敌手</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>术杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="7" tint="0.39997558519241921"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>法咒式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>带来的异常状态，破增加30+GR*3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>武杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>直接造成伤害时根据行动加快效果提升伤害共{[int]}%，行动加快{[int]}息</t>
+    </r>
+  </si>
+  <si>
+    <t>每层使行动延迟{[int]}息</t>
+  </si>
+  <si>
+    <t>增益状态无法生效，每层使行动延迟{[int]}息</t>
+  </si>
+  <si>
+    <t>出招时无法使用↑键</t>
+  </si>
+  <si>
+    <t>出招时无法使用↓键</t>
+  </si>
+  <si>
+    <t>出招时无法使用←键</t>
+  </si>
+  <si>
+    <t>出招时无法使用→键</t>
+  </si>
+  <si>
+    <t>行动的意图被揭示</t>
+  </si>
+  <si>
+    <t>每层使扣除键时同时扣除{[int]}的体</t>
+  </si>
+  <si>
+    <t>无法使用4键招式</t>
+  </si>
+  <si>
+    <t>无法使用变式</t>
+  </si>
+  <si>
+    <t>使用招式每消耗1个↑键减少1层妖毒侵蚀状态与妖毒状态</t>
+  </si>
+  <si>
+    <t>使用招式每消耗1个→键减少1层妖毒侵蚀状态与妖毒状态</t>
+  </si>
+  <si>
+    <t>使用招式每消耗1个↓键减少1层妖毒侵蚀状态与妖毒状态</t>
+  </si>
+  <si>
+    <t>使用招式每消耗1个←键减少1层妖毒侵蚀状态与妖毒状态</t>
+  </si>
+  <si>
+    <t>无法获得增益状态</t>
+  </si>
+  <si>
+    <t>施加者受到伤害时扣除伤害量{[int]}%的体</t>
+  </si>
+  <si>
+    <t>每层使玄炁消耗增加{[int]}</t>
+  </si>
+  <si>
+    <t>无法使用招式</t>
+  </si>
+  <si>
+    <t>该消除时扣除65+GR*13的体</t>
+  </si>
+  <si>
+    <t>无法使用招式，受到招式的直接攻击或被消除时扣除2层</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>每层使获得的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>刚炁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>减少{[int]}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>每层使获得的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>玄炁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>减少{[int]}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>每层使</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>减少{[int]}%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>每层使</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>技</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>减少{[int]}%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>每层使</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>武杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>威力减少{[int]}的百分比</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>每层使</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>术杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>威力减少{[int]}的百分比</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>减少</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>武杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>{[int]}%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>的直接伤害，减少对非交锋目标的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>术杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>{[int]}%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>技</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>的直接伤害</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>无法使用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>武杀式</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>无法使用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>术杀式</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>无法使用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>技御式</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>无法使用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="7" tint="0.39997558519241921"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>法咒式</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>行动开始</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>在本次行动中随机污染x个键，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>使用招式每消耗1个被污染的键</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>获得1层妖毒侵蚀状态（正常的键优先消耗），因任何原因减少被污染的键时等量减少妖毒状态的层数</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>每次获得该状态</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>扣除</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>层数*2%的当前命</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>回合结束时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>扣除10+GR*2的体上限并恢复等量的体</t>
+    </r>
+  </si>
+  <si>
+    <t>行动加快8息</t>
+  </si>
+  <si>
+    <t>可使用猊煞变派系招式</t>
+  </si>
+  <si>
+    <t>允许消耗体上限21+GR*3：1替代刚炁的消耗，消耗至多不能超过当前已损生命</t>
+  </si>
+  <si>
+    <t>武杀式、术杀式威力提升，越弱的招式越多。技御式、法咒式刚炁或玄炁消耗减少（取最高的一项减少）</t>
+  </si>
+  <si>
+    <t>招式的力或技取值从角色自身属性改为250+GR*25</t>
+  </si>
+  <si>
+    <t>无法直接清除异常状态</t>
+  </si>
+  <si>
+    <t>下一次行动中恢复刚炁时获得等量玄炁，恢复玄炁时获得等量刚炁</t>
+  </si>
+  <si>
+    <t>属性能够与他人交换（该buff所记录的基础属性已覆盖持有者自身基础属性）</t>
+  </si>
+  <si>
+    <t>下一次术杀式的基础伤害不会低于140%技</t>
+  </si>
+  <si>
+    <t>每层使键上限减少1</t>
+  </si>
+  <si>
+    <t>力提升15%，防提升15%，层数大于4效果翻倍并变身为兽</t>
+  </si>
+  <si>
+    <t>巧提升15%，速提升15%，层数大于4效果翻倍并变身为禽</t>
+  </si>
+  <si>
+    <t>技提升15%，破提升15%，层数大于4效果翻倍并变身为祖</t>
+  </si>
+  <si>
+    <t>武杀式行动觉决定后威力提升不会低于该状态*5的百分比，每层使回合结束扣除20+GR*4的体并增加1层烈命状态</t>
+  </si>
+  <si>
+    <t>被击破时随机转移至另一个友方，若是术杀式击破则扣除1层，完全清除时结束战斗</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>回合开始</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>层数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>超过3则清除该状态并</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>刚炁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>+{[int]}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>受到攻击后</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>对攻击者造成其等级挂钩的伤害</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>每20层使</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF92D050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>速</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>-{[int]}，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>+{[int]}，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>技</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>+{[int]}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>若受到</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>的直接攻击所削减体，本次行动失败（消耗行动所需的炁，触发行动后扳机）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>我方杀式命中时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>消耗1层敷宵剑状态</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>对其目标释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>术杀式：敷宵剑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>，三息内至多释放一次</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>敷宵剑交锋后</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>施加2层</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>力衰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>状态</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>{[int]}受到单方面杀式攻击前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>消耗1层敷宵剑状态</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>，对其释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>术杀式：敷宵剑</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>术杀式：敷宵剑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>威力增加效果翻倍，威力增加35%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>下次行动时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>若首个键为↑或→则获得额外回合，且行动是首个键为↑的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>非武杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>或是首个键为→的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>武杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>则获得3个随机的键</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>下次行动时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>若首个键为→或↓则获得额外回合，且行动是首个键为→的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>非武杀式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>或是首个键为↓的武杀式则获得3个随机的键</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>下次行动时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>若首个键为↓或←则获得额外回合，且行动是首个键为↓的非武杀式或是首个键为←的武杀式则获得3个随机的键</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>下次行动时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>若首个键为←或↑则获得额外回合，且行动是首个键为←的非武杀式或是首个键为↑的武杀式则获得3个随机的键</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>下次行动时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>若首个键为↑或→则获得额外回合，且行动是首个键为↑的非术杀式或是首个键为→的术杀式则获得3个随机的键</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>下次行动时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>若首个键为→或↓则获得额外回合，且行动是首个键为→的非术杀式或是首个键为↓的术杀式则获得3个随机的键</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>下次行动时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>若首个键为↓或←则获得额外回合，且行动是首个键为↓的非术杀式或是首个键为←的术杀式则获得3个随机的键</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>下次行动时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>若首个键为←或↑则获得额外回合，且行动是首个键为←的非术杀式或是首个键为↑的术杀式则获得3个随机的键</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>下次行动时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>若首个键为↑或→则获得额外回合，且行动是首个键为↑的非技御式或是首个键为→的技御式则获得3个随机的键</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>下次行动时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>若首个键为→或↓则获得额外回合，且行动是首个键为→的非技御式或是首个键为↓的技御式则获得3个随机的键</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>下次行动时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>若首个键为↓或←则获得额外回合，且行动是首个键为↓的非技御式或是首个键为←的技御式则获得3个随机的键</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>下次行动时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>若首个键为←或↑则获得额外回合，且行动是首个键为←的非技御式或是首个键为↑的技御式则获得3个随机的键</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>下次行动时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>若首个键为↑或→则获得额外回合，且行动是首个键为↑的非法咒式或是首个键为→的法咒式则获得3个随机的键</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>下次行动时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>若首个键为→或↓则获得额外回合，且行动是首个键为→的非法咒式或是首个键为↓的法咒式则获得3个随机的键</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>下次行动时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>若首个键为↓或←则获得额外回合，且行动是首个键为↓的非法咒式或是首个键为←的法咒式则获得3个随机的键</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>下次行动时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>若首个键为←或↑则获得额外回合，且行动是首个键为←的非法咒式或是首个键为↑的法咒式则获得3个随机的键</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>命</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>低于30%即死</t>
+    </r>
+  </si>
+  <si>
+    <t>行动开始固定增加5刚炁</t>
+  </si>
+  <si>
+    <t>行动开始固定增加5玄炁</t>
+  </si>
+  <si>
+    <t>回合开始固定增加7玄炁</t>
+  </si>
+  <si>
+    <t>回合开始固定增加25玄炁</t>
+  </si>
+  <si>
+    <t>行动开始固定增加9玄炁</t>
+  </si>
+  <si>
+    <t>回合开始固定增加12玄炁</t>
+  </si>
+  <si>
+    <t>行动结束获得1个随机的键</t>
+  </si>
+  <si>
+    <t>回合结束获得1个随机的键</t>
+  </si>
+  <si>
+    <t>回合结束获得4个随机的键</t>
+  </si>
+  <si>
+    <t>回合结束获得4个↑键</t>
+  </si>
+  <si>
+    <t>回合结束获得4个↓键</t>
+  </si>
+  <si>
+    <t>回合结束获得4个←键</t>
+  </si>
+  <si>
+    <t>回合结束获得4个→键</t>
+  </si>
+  <si>
+    <t>回合结束固定恢复35+GR*7体</t>
+  </si>
+  <si>
+    <t>回合结束固定恢复175+GR*25体</t>
+  </si>
+  <si>
+    <t>速提升20+GR*1</t>
+  </si>
+  <si>
+    <t>力提升40+GR*2</t>
+  </si>
+  <si>
+    <t>技提升40+GR*2</t>
+  </si>
+  <si>
+    <t>破提升14+GR*0.7</t>
+  </si>
+  <si>
+    <t>防提升14+GR*0.7</t>
+  </si>
+  <si>
+    <t>巧提升20+GR*1</t>
+  </si>
+  <si>
+    <t>速提升10+GR*0.5</t>
+  </si>
+  <si>
+    <t>巧提升10+GR*0.5</t>
+  </si>
+  <si>
+    <r>
+      <t>回合开始</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>固定增加{[int]}刚炁</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>行动开始</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>固定增加{[int]}刚炁</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>行动决定后</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>揭示目标直到下{[int]}息内的已决定行动</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>心眼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CalculateActionWheelMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算息的时候扳机调用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每层使行动加快1息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>每层使获得的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>刚炁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>增加1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>每层使获得的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>玄炁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>增加1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>每层使</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>增加10%</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>每层使</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>技</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>增加10%</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每层使巧增加10%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11,6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>护盾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>甲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>延迟甲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleBuffArmor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleBuffArmorDelay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特殊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>99999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>80001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>80002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>81001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>81002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下回合开始移除所有键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffAddLayerMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffStartMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加buff只触发一次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffRemoveMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff移除扳机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每层使刚炁消耗增加{[int]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合开始减少一层</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(回合开始添加盾,扳机ID)延迟盾的触发扳机,触发后清空层数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(回合开始添加甲,扳机ID)延迟甲的触发扳机,触发后清空层数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900031</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900012</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900022</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90041</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckSkillDoDesition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckSkillDoDesitionRelation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断技能能否释放或与（1与，2或）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>避殃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下次行动玄气消耗减少30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动后减少一层（一般默认两层）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900051</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900052</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下次行动决定后行动次数加1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动决定后减少1层</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900061</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>猊煞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>毒瘴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>因招式获得的气减少100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动后清空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900071</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900072</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>破招抵免</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抵免1次破招</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下回合猊煞不会产生消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900081</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900082</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>息结束的扳机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActionWheelEndMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>反击buff三息内不会低于1层</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>19,1,11,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>息结束减少一层，回合结束清空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900091</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900092</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本回合下次行动术杀式威力+15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,2,11,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动后清空，回合结束清空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>寒沁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技式禁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本次行动威力+10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900111</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900112</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赤沸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单独脚本buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每有一个键该招式威力增加5的百分比</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleBuffChangeTempSkillDamageRateByKeyCount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本次交锋不会被破招</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleBuffDontBeCounter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本次交锋不会被被未带有↓类留劲状态的敌手破招</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本次交锋不会被被未带有↑类留劲状态的敌手破招</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本次交锋不会被被未带有←类留劲状态的敌手破招</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本次交锋不会被被未带有→类留劲状态的敌手破招</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>封穴↑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9,2,10,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>隐魂</t>
-  </si>
-  <si>
-    <t>雷行</t>
-  </si>
-  <si>
-    <t>行字诀</t>
-  </si>
-  <si>
-    <t>匿形</t>
-  </si>
-  <si>
-    <t>借法</t>
-  </si>
-  <si>
-    <t>岳环架势</t>
-  </si>
-  <si>
-    <t>御守架势</t>
-  </si>
-  <si>
-    <t>龙腾</t>
-  </si>
-  <si>
-    <t>回春</t>
-  </si>
-  <si>
-    <t>缓速</t>
-  </si>
-  <si>
-    <t>失衡</t>
-  </si>
-  <si>
-    <t>封穴↑</t>
-  </si>
-  <si>
-    <t>封穴↓</t>
-  </si>
-  <si>
-    <t>封穴←</t>
-  </si>
-  <si>
-    <t>封穴→</t>
-  </si>
-  <si>
-    <t>破绽</t>
-  </si>
-  <si>
-    <t>伤口</t>
-  </si>
-  <si>
-    <t>刚屏</t>
-  </si>
-  <si>
-    <t>玄屏</t>
-  </si>
-  <si>
-    <t>力衰</t>
-  </si>
-  <si>
-    <t>技衰</t>
-  </si>
-  <si>
-    <t>武衰</t>
-  </si>
-  <si>
-    <t>术衰</t>
-  </si>
-  <si>
-    <t>僵硬</t>
-  </si>
-  <si>
-    <t>过劲</t>
-  </si>
-  <si>
-    <t>盲目</t>
-  </si>
-  <si>
-    <t>武式禁</t>
-  </si>
-  <si>
-    <t>术式禁</t>
-  </si>
-  <si>
-    <t>法式禁</t>
-  </si>
-  <si>
-    <t>妖毒</t>
-  </si>
-  <si>
-    <t>妖毒侵蚀</t>
-  </si>
-  <si>
-    <t>毒向↑</t>
-  </si>
-  <si>
-    <t>毒向→</t>
-  </si>
-  <si>
-    <t>毒向↓</t>
-  </si>
-  <si>
-    <t>毒向←</t>
-  </si>
-  <si>
-    <t>失持</t>
-  </si>
-  <si>
-    <t>共生</t>
-  </si>
-  <si>
-    <t>晕眩</t>
-  </si>
-  <si>
-    <t>苦印</t>
-  </si>
-  <si>
-    <t>昏沉</t>
-  </si>
-  <si>
-    <t>交鸣</t>
-  </si>
-  <si>
-    <t>先发制人</t>
-  </si>
-  <si>
-    <t>异鳞</t>
-  </si>
-  <si>
-    <t>饕餮万物</t>
-  </si>
-  <si>
-    <t>破招</t>
-  </si>
-  <si>
-    <t>敷宵剑</t>
-  </si>
-  <si>
-    <t>断筋式</t>
-  </si>
-  <si>
-    <t>傍剑</t>
-  </si>
-  <si>
-    <t>御敌式</t>
-  </si>
-  <si>
-    <t>留劲·武杀式↑</t>
-  </si>
-  <si>
-    <t>留劲·武杀式→</t>
-  </si>
-  <si>
-    <t>留劲·武杀式↓</t>
-  </si>
-  <si>
-    <t>留劲·武杀式←</t>
-  </si>
-  <si>
-    <t>留劲·术杀式↑</t>
-  </si>
-  <si>
-    <t>留劲·术杀式→</t>
-  </si>
-  <si>
-    <t>留劲·术杀式↓</t>
-  </si>
-  <si>
-    <t>留劲·术杀式←</t>
-  </si>
-  <si>
-    <t>留劲·技杀式↑</t>
-  </si>
-  <si>
-    <t>留劲·技御式→</t>
-  </si>
-  <si>
-    <t>留劲·技御式↓</t>
-  </si>
-  <si>
-    <t>留劲·技御式←</t>
-  </si>
-  <si>
-    <t>留劲·法咒式↑</t>
-  </si>
-  <si>
-    <t>留劲·法咒式→</t>
-  </si>
-  <si>
-    <t>留劲·法咒式↓</t>
-  </si>
-  <si>
-    <t>留劲·法咒式←</t>
-  </si>
-  <si>
-    <t>死楔</t>
-  </si>
-  <si>
-    <t>燃息</t>
-  </si>
-  <si>
-    <t>平</t>
-  </si>
-  <si>
-    <t>彻</t>
-  </si>
-  <si>
-    <t>起</t>
-  </si>
-  <si>
-    <t>固灾</t>
-  </si>
-  <si>
-    <t>玉摄念</t>
-  </si>
-  <si>
-    <t>戴面</t>
-  </si>
-  <si>
-    <t>巧来方计</t>
-  </si>
-  <si>
-    <t>残缺</t>
-  </si>
-  <si>
-    <t>兽化身</t>
-  </si>
-  <si>
-    <t>禽化身</t>
-  </si>
-  <si>
-    <t>祖化身</t>
-  </si>
-  <si>
-    <t>烈命</t>
-  </si>
-  <si>
-    <t>瘴鬼本源</t>
-  </si>
-  <si>
-    <t>药力·刚炁恢复</t>
-  </si>
-  <si>
-    <t>药力·玄炁恢复</t>
-  </si>
-  <si>
-    <t>药力·稳势</t>
-  </si>
-  <si>
-    <t>药力·体恢复</t>
-  </si>
-  <si>
-    <t>药力·速</t>
-  </si>
-  <si>
-    <t>药力·力</t>
-  </si>
-  <si>
-    <t>药力·技</t>
-  </si>
-  <si>
-    <t>药力·破</t>
-  </si>
-  <si>
-    <t>药力·防</t>
-  </si>
-  <si>
-    <t>药力·巧</t>
-  </si>
-  <si>
-    <t>行动后获得1个随机的键</t>
-  </si>
-  <si>
-    <t>无法成为行动的目标</t>
-  </si>
-  <si>
-    <t>无法被施加异常状态</t>
-  </si>
-  <si>
-    <t>玄炁上限增加10</t>
-  </si>
-  <si>
-    <t>若可以成为行动目标，则其余友方无法成为行动目标</t>
-  </si>
-  <si>
-    <t>全部的破、防的提升效果增加30%</t>
-  </si>
-  <si>
-    <t>回合开始扣除1层异常状态并获得{[int]}层护体，该状态被清除时只会扣除2层</t>
-  </si>
-  <si>
-    <t>行动后扣除1层该状态并恢复30+gr*6体，在下1息转移至包括自身首个行动的友方目标，若没有发生转移或被消除时扣除2层</t>
-  </si>
-  <si>
-    <r>
-      <t>至少减少受到的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>武杀式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>{[int]}%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>敌手的力</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>的直接伤害，至少减少行动目标对自身的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>术杀式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>伤害{[int]}%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>敌手的技</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>的直接伤害</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>受到攻击后</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>自身未存在行动则消耗一层</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF92D050"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>反击</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>状态对其使用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>武杀式：反击</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>每层使</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>武杀式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>威力增加5百分比</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>每层使</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>术杀式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>威力增加5百分比</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>抵免{[int]}次敌手</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>武杀式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="9" tint="0.39997558519241921"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>技御式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>带来的异常状态，防增加30+GR*3</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>抵免{[int]}次敌手</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>术杀式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="7" tint="0.39997558519241921"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>法咒式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>带来的异常状态，破增加30+GR*3</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>武杀式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>直接造成伤害时根据行动加快效果提升伤害共{[int]}%，行动加快{[int]}息</t>
-    </r>
-  </si>
-  <si>
-    <t>每层使行动延迟{[int]}息</t>
-  </si>
-  <si>
-    <t>增益状态无法生效，每层使行动延迟{[int]}息</t>
-  </si>
-  <si>
-    <t>出招时无法使用↑键</t>
-  </si>
-  <si>
-    <t>出招时无法使用↓键</t>
-  </si>
-  <si>
-    <t>出招时无法使用←键</t>
-  </si>
-  <si>
-    <t>出招时无法使用→键</t>
-  </si>
-  <si>
-    <t>行动的意图被揭示</t>
-  </si>
-  <si>
-    <t>每层使扣除键时同时扣除{[int]}的体</t>
-  </si>
-  <si>
-    <t>无法使用4键招式</t>
-  </si>
-  <si>
-    <t>无法使用变式</t>
-  </si>
-  <si>
-    <t>使用招式每消耗1个↑键减少1层妖毒侵蚀状态与妖毒状态</t>
-  </si>
-  <si>
-    <t>使用招式每消耗1个→键减少1层妖毒侵蚀状态与妖毒状态</t>
-  </si>
-  <si>
-    <t>使用招式每消耗1个↓键减少1层妖毒侵蚀状态与妖毒状态</t>
-  </si>
-  <si>
-    <t>使用招式每消耗1个←键减少1层妖毒侵蚀状态与妖毒状态</t>
-  </si>
-  <si>
-    <t>无法获得增益状态</t>
-  </si>
-  <si>
-    <t>施加者受到伤害时扣除伤害量{[int]}%的体</t>
-  </si>
-  <si>
-    <t>每层使玄炁消耗增加{[int]}</t>
-  </si>
-  <si>
-    <t>无法使用招式</t>
-  </si>
-  <si>
-    <t>该消除时扣除65+GR*13的体</t>
-  </si>
-  <si>
-    <t>无法使用招式，受到招式的直接攻击或被消除时扣除2层</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>每层使获得的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>刚炁</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>减少{[int]}</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>每层使获得的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>玄炁</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>减少{[int]}</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>每层使</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>力</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>减少{[int]}%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>每层使</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>技</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>减少{[int]}%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>每层使</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>武杀式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>威力减少{[int]}的百分比</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>每层使</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>术杀式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>威力减少{[int]}的百分比</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>减少</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>武杀式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>{[int]}%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>力</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>的直接伤害，减少对非交锋目标的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>术杀式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>{[int]}%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>技</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>的直接伤害</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>无法使用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>武杀式</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>无法使用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>术杀式</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>无法使用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="9" tint="-0.249977111117893"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>技御式</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>无法使用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="7" tint="0.39997558519241921"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>法咒式</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>行动开始</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>在本次行动中随机污染x个键，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>使用招式每消耗1个被污染的键</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>获得1层妖毒侵蚀状态（正常的键优先消耗），因任何原因减少被污染的键时等量减少妖毒状态的层数</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>每次获得该状态</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>扣除</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>层数*2%的当前命</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>回合结束时</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>扣除10+GR*2的体上限并恢复等量的体</t>
-    </r>
-  </si>
-  <si>
-    <t>行动加快8息</t>
-  </si>
-  <si>
-    <t>可使用猊煞变派系招式</t>
-  </si>
-  <si>
-    <t>允许消耗体上限21+GR*3：1替代刚炁的消耗，消耗至多不能超过当前已损生命</t>
-  </si>
-  <si>
-    <t>武杀式、术杀式威力提升，越弱的招式越多。技御式、法咒式刚炁或玄炁消耗减少（取最高的一项减少）</t>
-  </si>
-  <si>
-    <t>招式的力或技取值从角色自身属性改为250+GR*25</t>
-  </si>
-  <si>
-    <t>无法直接清除异常状态</t>
-  </si>
-  <si>
-    <t>下一次行动中恢复刚炁时获得等量玄炁，恢复玄炁时获得等量刚炁</t>
-  </si>
-  <si>
-    <t>属性能够与他人交换（该buff所记录的基础属性已覆盖持有者自身基础属性）</t>
-  </si>
-  <si>
-    <t>下一次术杀式的基础伤害不会低于140%技</t>
-  </si>
-  <si>
-    <t>每层使键上限减少1</t>
-  </si>
-  <si>
-    <t>力提升15%，防提升15%，层数大于4效果翻倍并变身为兽</t>
-  </si>
-  <si>
-    <t>巧提升15%，速提升15%，层数大于4效果翻倍并变身为禽</t>
-  </si>
-  <si>
-    <t>技提升15%，破提升15%，层数大于4效果翻倍并变身为祖</t>
-  </si>
-  <si>
-    <t>武杀式行动觉决定后威力提升不会低于该状态*5的百分比，每层使回合结束扣除20+GR*4的体并增加1层烈命状态</t>
-  </si>
-  <si>
-    <t>被击破时随机转移至另一个友方，若是术杀式击破则扣除1层，完全清除时结束战斗</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>回合开始</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>层数</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>超过3则清除该状态并</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>刚炁</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>+{[int]}</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>受到攻击后</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>对攻击者造成其等级挂钩的伤害</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>每20层使</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF92D050"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>速</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>-{[int]}，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>力</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>+{[int]}，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>技</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>+{[int]}</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>若受到</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="9" tint="-0.249977111117893"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>杀式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>的直接攻击所削减体，本次行动失败（消耗行动所需的炁，触发行动后扳机）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>我方杀式命中时</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>消耗1层敷宵剑状态</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>对其目标释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>术杀式：敷宵剑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>，三息内至多释放一次</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>敷宵剑交锋后</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>施加2层</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="0" tint="-0.499984740745262"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>力衰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>状态</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>{[int]}受到单方面杀式攻击前</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>消耗1层敷宵剑状态</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>，对其释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>术杀式：敷宵剑</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>术杀式：敷宵剑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>威力增加效果翻倍，威力增加35%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>下次行动时</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>若首个键为↑或→则获得额外回合，且行动是首个键为↑的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>非武杀式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>或是首个键为→的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>武杀式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>则获得3个随机的键</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>下次行动时</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>若首个键为→或↓则获得额外回合，且行动是首个键为→的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>非武杀式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>或是首个键为↓的武杀式则获得3个随机的键</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>下次行动时</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>若首个键为↓或←则获得额外回合，且行动是首个键为↓的非武杀式或是首个键为←的武杀式则获得3个随机的键</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>下次行动时</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>若首个键为←或↑则获得额外回合，且行动是首个键为←的非武杀式或是首个键为↑的武杀式则获得3个随机的键</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>下次行动时</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>若首个键为↑或→则获得额外回合，且行动是首个键为↑的非术杀式或是首个键为→的术杀式则获得3个随机的键</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>下次行动时</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>若首个键为→或↓则获得额外回合，且行动是首个键为→的非术杀式或是首个键为↓的术杀式则获得3个随机的键</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>下次行动时</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>若首个键为↓或←则获得额外回合，且行动是首个键为↓的非术杀式或是首个键为←的术杀式则获得3个随机的键</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>下次行动时</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>若首个键为←或↑则获得额外回合，且行动是首个键为←的非术杀式或是首个键为↑的术杀式则获得3个随机的键</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>下次行动时</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>若首个键为↑或→则获得额外回合，且行动是首个键为↑的非技御式或是首个键为→的技御式则获得3个随机的键</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>下次行动时</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>若首个键为→或↓则获得额外回合，且行动是首个键为→的非技御式或是首个键为↓的技御式则获得3个随机的键</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>下次行动时</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>若首个键为↓或←则获得额外回合，且行动是首个键为↓的非技御式或是首个键为←的技御式则获得3个随机的键</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>下次行动时</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>若首个键为←或↑则获得额外回合，且行动是首个键为←的非技御式或是首个键为↑的技御式则获得3个随机的键</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>下次行动时</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>若首个键为↑或→则获得额外回合，且行动是首个键为↑的非法咒式或是首个键为→的法咒式则获得3个随机的键</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>下次行动时</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>若首个键为→或↓则获得额外回合，且行动是首个键为→的非法咒式或是首个键为↓的法咒式则获得3个随机的键</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>下次行动时</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>若首个键为↓或←则获得额外回合，且行动是首个键为↓的非法咒式或是首个键为←的法咒式则获得3个随机的键</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>下次行动时</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>若首个键为←或↑则获得额外回合，且行动是首个键为←的非法咒式或是首个键为↑的法咒式则获得3个随机的键</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>命</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>低于30%即死</t>
-    </r>
-  </si>
-  <si>
-    <t>行动开始固定增加5刚炁</t>
-  </si>
-  <si>
-    <t>行动开始固定增加5玄炁</t>
-  </si>
-  <si>
-    <t>回合开始固定增加7玄炁</t>
-  </si>
-  <si>
-    <t>回合开始固定增加25玄炁</t>
-  </si>
-  <si>
-    <t>行动开始固定增加9玄炁</t>
-  </si>
-  <si>
-    <t>回合开始固定增加12玄炁</t>
-  </si>
-  <si>
-    <t>行动结束获得1个随机的键</t>
-  </si>
-  <si>
-    <t>回合结束获得1个随机的键</t>
-  </si>
-  <si>
-    <t>回合结束获得4个随机的键</t>
-  </si>
-  <si>
-    <t>回合结束获得4个↑键</t>
-  </si>
-  <si>
-    <t>回合结束获得4个↓键</t>
-  </si>
-  <si>
-    <t>回合结束获得4个←键</t>
-  </si>
-  <si>
-    <t>回合结束获得4个→键</t>
-  </si>
-  <si>
-    <t>回合结束固定恢复35+GR*7体</t>
-  </si>
-  <si>
-    <t>回合结束固定恢复175+GR*25体</t>
-  </si>
-  <si>
-    <t>速提升20+GR*1</t>
-  </si>
-  <si>
-    <t>力提升40+GR*2</t>
-  </si>
-  <si>
-    <t>技提升40+GR*2</t>
-  </si>
-  <si>
-    <t>破提升14+GR*0.7</t>
-  </si>
-  <si>
-    <t>防提升14+GR*0.7</t>
-  </si>
-  <si>
-    <t>巧提升20+GR*1</t>
-  </si>
-  <si>
-    <t>速提升10+GR*0.5</t>
-  </si>
-  <si>
-    <t>巧提升10+GR*0.5</t>
-  </si>
-  <si>
-    <r>
-      <t>回合开始</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>固定增加{[int]}刚炁</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>行动开始</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>固定增加{[int]}刚炁</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>行动决定后</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>揭示目标直到下{[int]}息内的已决定行动</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>心眼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CalculateActionWheelMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计算息的时候扳机调用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每层使行动加快1息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>每层使获得的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>刚炁</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>增加1</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>每层使获得的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>玄炁</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>增加1</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>每层使</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>力</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>增加10%</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>每层使</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>技</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>增加10%</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每层使巧增加10%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>99</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11,6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10,6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10,5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>护盾</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>甲</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>延迟甲</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleBuffArmor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleBuffArmorDelay</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BuffType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Buff类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>特殊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>99999</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>80001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>80002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>81001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>81002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>90001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>90002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>90003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>90004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>下回合开始移除所有键</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BuffAddLayerMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BuffStartMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>添加buff只触发一次</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BuffRemoveMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>buff移除扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每层使刚炁消耗增加{[int]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合开始减少一层</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(回合开始添加盾,扳机ID)延迟盾的触发扳机,触发后清空层数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(回合开始添加甲,扳机ID)延迟甲的触发扳机,触发后清空层数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>900031</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>900011</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>900012</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>900021</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>900022</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>90041</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CheckSkillDoDesition</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CheckSkillDoDesitionRelation</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>判断技能能否释放或与（1与，2或）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>避殃</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>90005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>下次行动玄气消耗减少30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>行动后减少一层（一般默认两层）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>900051</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>900052</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>90006</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>下次行动决定后行动次数加1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>行动决定后减少1层</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>900061</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>猊煞</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>毒瘴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>90007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>因招式获得的气减少100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>行动后清空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>900071</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>900072</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>破招抵免</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>抵免1次破招</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>90008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>下回合猊煞不会产生消耗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>900081</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>900082</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>息结束的扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActionWheelEndMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>90009</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>反击buff三息内不会低于1层</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>19,1,11,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>息结束减少一层，回合结束清空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>900091</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>900092</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>90010</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>本回合下次行动术杀式威力+15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10,2,11,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>行动后清空，回合结束清空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>900101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>900102</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>寒沁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技式禁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>90011</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>本次行动威力+10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>900111</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>900112</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>赤沸</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>单独脚本buff</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每有一个键该招式威力增加5的百分比</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleBuffChangeTempSkillDamageRateByKeyCount</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90012</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下次行动刚气消耗减少30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900121</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900122</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2909,7 +2963,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2939,6 +2993,9 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3254,13 +3311,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:AE196"/>
+  <dimension ref="A1:AE201"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.75" style="1" customWidth="1"/>
     <col min="3" max="3" width="29.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="158.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="66.375" style="1" customWidth="1"/>
     <col min="5" max="5" width="53.125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="25.875" style="1" customWidth="1"/>
     <col min="7" max="7" width="13.375" style="1" bestFit="1" customWidth="1"/>
@@ -3308,7 +3365,7 @@
         <v>44</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>37</v>
@@ -3326,16 +3383,16 @@
         <v>69</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>18</v>
@@ -3344,7 +3401,7 @@
         <v>20</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>10</v>
@@ -3374,16 +3431,16 @@
         <v>13</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AC1" s="1" t="s">
         <v>22</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
@@ -3495,7 +3552,7 @@
         <v>45</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>38</v>
@@ -3510,7 +3567,7 @@
         <v>68</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>41</v>
@@ -3519,7 +3576,7 @@
         <v>39</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>19</v>
@@ -3528,7 +3585,7 @@
         <v>21</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="S3" s="1" t="s">
         <v>14</v>
@@ -3558,7 +3615,7 @@
         <v>24</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AC3" s="1" t="s">
         <v>23</v>
@@ -3567,7 +3624,7 @@
         <v>36</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -3575,10 +3632,10 @@
         <v>10011</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>46</v>
@@ -3587,10 +3644,10 @@
         <v>62</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.2">
@@ -3601,7 +3658,7 @@
         <v>72</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>46</v>
@@ -3624,7 +3681,7 @@
         <v>73</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>46</v>
@@ -3633,7 +3690,7 @@
         <v>62</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>50</v>
@@ -3647,7 +3704,7 @@
         <v>74</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>46</v>
@@ -3656,10 +3713,10 @@
         <v>62</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.2">
@@ -3670,7 +3727,7 @@
         <v>75</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>46</v>
@@ -3679,7 +3736,7 @@
         <v>62</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>66</v>
@@ -3693,7 +3750,7 @@
         <v>76</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>46</v>
@@ -3702,7 +3759,7 @@
         <v>62</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>66</v>
@@ -3716,7 +3773,7 @@
         <v>77</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>46</v>
@@ -3725,10 +3782,10 @@
         <v>62</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
@@ -3739,7 +3796,7 @@
         <v>78</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>46</v>
@@ -3748,10 +3805,10 @@
         <v>62</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
@@ -3762,7 +3819,7 @@
         <v>79</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>46</v>
@@ -3771,10 +3828,10 @@
         <v>62</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
@@ -3785,7 +3842,7 @@
         <v>80</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>46</v>
@@ -3794,10 +3851,10 @@
         <v>62</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
@@ -3808,7 +3865,7 @@
         <v>81</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>46</v>
@@ -3817,10 +3874,10 @@
         <v>62</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.2">
@@ -3831,7 +3888,7 @@
         <v>82</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>46</v>
@@ -3843,7 +3900,7 @@
         <v>48</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
@@ -3851,10 +3908,10 @@
         <v>10131</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>83</v>
+        <v>401</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>46</v>
@@ -3871,10 +3928,10 @@
         <v>10141</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>46</v>
@@ -3883,10 +3940,10 @@
         <v>62</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -3894,10 +3951,10 @@
         <v>10151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>46</v>
@@ -3909,7 +3966,7 @@
         <v>48</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
@@ -3917,10 +3974,10 @@
         <v>10161</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>46</v>
@@ -3932,7 +3989,7 @@
         <v>48</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.2">
@@ -3940,10 +3997,10 @@
         <v>10171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>46</v>
@@ -3955,7 +4012,7 @@
         <v>48</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -3963,10 +4020,10 @@
         <v>10181</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>46</v>
@@ -3975,10 +4032,10 @@
         <v>62</v>
       </c>
       <c r="H22" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.2">
@@ -3986,10 +4043,10 @@
         <v>10191</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>46</v>
@@ -4001,7 +4058,7 @@
         <v>48</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -4009,10 +4066,10 @@
         <v>10201</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>46</v>
@@ -4024,7 +4081,7 @@
         <v>48</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
@@ -4032,10 +4089,10 @@
         <v>10211</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>46</v>
@@ -4055,10 +4112,10 @@
         <v>10221</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>46</v>
@@ -4067,10 +4124,10 @@
         <v>62</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="27" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -4079,10 +4136,10 @@
         <v>20011</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>46</v>
@@ -4094,7 +4151,7 @@
         <v>10</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
@@ -4102,10 +4159,10 @@
         <v>20021</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>46</v>
@@ -4117,7 +4174,7 @@
         <v>8</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -4125,10 +4182,10 @@
         <v>20031</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>94</v>
+        <v>399</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>46</v>
@@ -4140,7 +4197,7 @@
         <v>1</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -4148,10 +4205,10 @@
         <v>20041</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>46</v>
@@ -4163,7 +4220,7 @@
         <v>1</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -4171,10 +4228,10 @@
         <v>20051</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>46</v>
@@ -4186,7 +4243,7 @@
         <v>1</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.2">
@@ -4194,10 +4251,10 @@
         <v>20061</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>46</v>
@@ -4209,7 +4266,7 @@
         <v>1</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.2">
@@ -4217,10 +4274,10 @@
         <v>20071</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>46</v>
@@ -4240,10 +4297,10 @@
         <v>20081</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>46</v>
@@ -4255,7 +4312,7 @@
         <v>1</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.2">
@@ -4263,10 +4320,10 @@
         <v>20091</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>46</v>
@@ -4286,10 +4343,10 @@
         <v>20101</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>46</v>
@@ -4309,10 +4366,10 @@
         <v>20111</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>46</v>
@@ -4324,7 +4381,7 @@
         <v>5</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.2">
@@ -4332,10 +4389,10 @@
         <v>20121</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>46</v>
@@ -4347,7 +4404,7 @@
         <v>5</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.2">
@@ -4355,10 +4412,10 @@
         <v>20131</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>46</v>
@@ -4370,7 +4427,7 @@
         <v>5</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.2">
@@ -4378,10 +4435,10 @@
         <v>20141</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>46</v>
@@ -4393,7 +4450,7 @@
         <v>5</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.2">
@@ -4401,10 +4458,10 @@
         <v>20151</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>46</v>
@@ -4424,10 +4481,10 @@
         <v>20161</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>46</v>
@@ -4439,7 +4496,7 @@
         <v>1</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.2">
@@ -4447,10 +4504,10 @@
         <v>20171</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>46</v>
@@ -4470,10 +4527,10 @@
         <v>20181</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>46</v>
@@ -4485,7 +4542,7 @@
         <v>1</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.2">
@@ -4493,10 +4550,10 @@
         <v>20191</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>46</v>
@@ -4508,7 +4565,7 @@
         <v>1</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.2">
@@ -4516,10 +4573,10 @@
         <v>20201</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>46</v>
@@ -4531,7 +4588,7 @@
         <v>1</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.2">
@@ -4539,10 +4596,10 @@
         <v>20211</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>46</v>
@@ -4554,7 +4611,7 @@
         <v>1</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.2">
@@ -4562,10 +4619,10 @@
         <v>20221</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>46</v>
@@ -4582,10 +4639,10 @@
         <v>20231</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>46</v>
@@ -4602,10 +4659,10 @@
         <v>20241</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>46</v>
@@ -4625,10 +4682,10 @@
         <v>20251</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>46</v>
@@ -4648,10 +4705,10 @@
         <v>20261</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>46</v>
@@ -4671,10 +4728,10 @@
         <v>20271</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>46</v>
@@ -4694,10 +4751,10 @@
         <v>20281</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>46</v>
@@ -4709,7 +4766,7 @@
         <v>1</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.2">
@@ -4717,10 +4774,10 @@
         <v>20291</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>46</v>
@@ -4740,10 +4797,10 @@
         <v>20301</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>46</v>
@@ -4755,7 +4812,7 @@
         <v>5</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.2">
@@ -4763,10 +4820,10 @@
         <v>20311</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>46</v>
@@ -4778,7 +4835,7 @@
         <v>5</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.2">
@@ -4786,10 +4843,10 @@
         <v>20321</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>46</v>
@@ -4801,7 +4858,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.2">
@@ -4809,10 +4866,10 @@
         <v>20331</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>46</v>
@@ -4832,10 +4889,10 @@
         <v>20341</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>46</v>
@@ -4852,10 +4909,10 @@
         <v>20351</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>46</v>
@@ -4867,7 +4924,7 @@
         <v>-1</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="63" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -4876,10 +4933,10 @@
         <v>30011</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>46</v>
@@ -4890,10 +4947,10 @@
         <v>30021</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>46</v>
@@ -4904,10 +4961,10 @@
         <v>30031</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>46</v>
@@ -4918,10 +4975,10 @@
         <v>30041</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>46</v>
@@ -4932,10 +4989,10 @@
         <v>30051</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>46</v>
@@ -4946,10 +5003,10 @@
         <v>30061</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>46</v>
@@ -4960,10 +5017,10 @@
         <v>30071</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>46</v>
@@ -4974,10 +5031,10 @@
         <v>30081</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>46</v>
@@ -4988,10 +5045,10 @@
         <v>30091</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>46</v>
@@ -5002,10 +5059,10 @@
         <v>30101</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>46</v>
@@ -5016,10 +5073,10 @@
         <v>30111</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>46</v>
@@ -5030,10 +5087,10 @@
         <v>30121</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>46</v>
@@ -5044,10 +5101,10 @@
         <v>30131</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>46</v>
@@ -5058,10 +5115,10 @@
         <v>30141</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>46</v>
@@ -5072,10 +5129,10 @@
         <v>30151</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>46</v>
@@ -5086,10 +5143,10 @@
         <v>30161</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>46</v>
@@ -5100,10 +5157,10 @@
         <v>30171</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>46</v>
@@ -5114,10 +5171,10 @@
         <v>30181</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>46</v>
@@ -5128,10 +5185,10 @@
         <v>30191</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>46</v>
@@ -5142,10 +5199,10 @@
         <v>30201</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>46</v>
@@ -5156,10 +5213,10 @@
         <v>30211</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>46</v>
@@ -5170,10 +5227,10 @@
         <v>30221</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>46</v>
@@ -5184,10 +5241,10 @@
         <v>30231</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>46</v>
@@ -5198,10 +5255,10 @@
         <v>30241</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>46</v>
@@ -5212,10 +5269,10 @@
         <v>30251</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>46</v>
@@ -5226,10 +5283,10 @@
         <v>30261</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>46</v>
@@ -5240,10 +5297,10 @@
         <v>30271</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>46</v>
@@ -5254,10 +5311,10 @@
         <v>30281</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>46</v>
@@ -5268,10 +5325,10 @@
         <v>30291</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>46</v>
@@ -5282,10 +5339,10 @@
         <v>30301</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>46</v>
@@ -5296,7 +5353,7 @@
         <v>30311</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" s="1" t="s">
@@ -5308,10 +5365,10 @@
         <v>30321</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>46</v>
@@ -5322,10 +5379,10 @@
         <v>30331</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>46</v>
@@ -5336,10 +5393,10 @@
         <v>30341</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>46</v>
@@ -5350,10 +5407,10 @@
         <v>30351</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>46</v>
@@ -5364,10 +5421,10 @@
         <v>30361</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>46</v>
@@ -5378,10 +5435,10 @@
         <v>30371</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>46</v>
@@ -5392,10 +5449,10 @@
         <v>30381</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>46</v>
@@ -5406,10 +5463,10 @@
         <v>30391</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>46</v>
@@ -5420,10 +5477,10 @@
         <v>30401</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>46</v>
@@ -5434,10 +5491,10 @@
         <v>30411</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>46</v>
@@ -5448,10 +5505,10 @@
         <v>30421</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>46</v>
@@ -5469,10 +5526,10 @@
         <v>40011</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>46</v>
@@ -5483,10 +5540,10 @@
         <v>40021</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D108" s="7" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>46</v>
@@ -5497,10 +5554,10 @@
         <v>40031</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>46</v>
@@ -5511,10 +5568,10 @@
         <v>40041</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>46</v>
@@ -5525,10 +5582,10 @@
         <v>40051</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>46</v>
@@ -5539,10 +5596,10 @@
         <v>40061</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>46</v>
@@ -5553,10 +5610,10 @@
         <v>40071</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>46</v>
@@ -5567,10 +5624,10 @@
         <v>40081</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>46</v>
@@ -5581,10 +5638,10 @@
         <v>40091</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>46</v>
@@ -5595,10 +5652,10 @@
         <v>40101</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>46</v>
@@ -5609,10 +5666,10 @@
         <v>40111</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>46</v>
@@ -5623,10 +5680,10 @@
         <v>40121</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>46</v>
@@ -5637,10 +5694,10 @@
         <v>40131</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>46</v>
@@ -5651,10 +5708,10 @@
         <v>40141</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>46</v>
@@ -5665,10 +5722,10 @@
         <v>40151</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>46</v>
@@ -5679,10 +5736,10 @@
         <v>40161</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>46</v>
@@ -5693,10 +5750,10 @@
         <v>40171</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>46</v>
@@ -5707,10 +5764,10 @@
         <v>40181</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>46</v>
@@ -5721,10 +5778,10 @@
         <v>40191</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>46</v>
@@ -5735,10 +5792,10 @@
         <v>40201</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>46</v>
@@ -5749,10 +5806,10 @@
         <v>40211</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>46</v>
@@ -5763,10 +5820,10 @@
         <v>40221</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>46</v>
@@ -5777,10 +5834,10 @@
         <v>40231</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>46</v>
@@ -5791,10 +5848,10 @@
         <v>40241</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>46</v>
@@ -5805,10 +5862,10 @@
         <v>40251</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>46</v>
@@ -5819,7 +5876,7 @@
         <v>40261</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>46</v>
@@ -5830,7 +5887,7 @@
         <v>40271</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>46</v>
@@ -5841,7 +5898,7 @@
         <v>40281</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>46</v>
@@ -5852,7 +5909,7 @@
         <v>40291</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>46</v>
@@ -5863,7 +5920,7 @@
         <v>40301</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>46</v>
@@ -5874,7 +5931,7 @@
         <v>40311</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>46</v>
@@ -6178,21 +6235,21 @@
     </row>
     <row r="175" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A175" s="9" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B176" s="2">
         <v>70001</v>
       </c>
-      <c r="C176" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>390</v>
+      <c r="C176" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="D176" s="10" t="s">
+        <v>388</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="G176" s="1" t="s">
         <v>47</v>
@@ -6201,236 +6258,259 @@
         <v>48</v>
       </c>
       <c r="I176" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="J176" s="1" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="177" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B177" s="2">
+        <v>71000</v>
+      </c>
+      <c r="C177" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="D177" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="G177" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H177" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I177" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="J177" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="178" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B178" s="2">
+        <v>71001</v>
+      </c>
+      <c r="C178" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="D178" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="G178" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H178" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I178" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="J178" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="179" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B179" s="2">
+        <v>71002</v>
+      </c>
+      <c r="C179" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="D179" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="G179" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H179" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I179" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="J179" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="180" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B180" s="2">
+        <v>71003</v>
+      </c>
+      <c r="C180" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="D180" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="G180" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H180" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I180" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="J180" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="181" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B181" s="2">
+        <v>71004</v>
+      </c>
+      <c r="C181" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="D181" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="G181" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H181" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I181" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="J181" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="182" spans="1:26" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A182" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="J176" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="177" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="B177" s="2"/>
-    </row>
-    <row r="178" spans="1:29" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A178" s="9" t="s">
+    </row>
+    <row r="183" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B183" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G183" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H183" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I183" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="184" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B184" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G184" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H184" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J184" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K184" s="1" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="185" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B185" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G185" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H185" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I185" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="186" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B186" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C186" s="1" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="179" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="B179" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="C179" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E179" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="G179" s="1" t="s">
+      <c r="D186" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="G186" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="H179" s="1" t="s">
+      <c r="H186" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="I179" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="180" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="B180" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="C180" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E180" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="G180" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H180" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J180" s="1" t="s">
+      <c r="J186" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K180" s="1" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="181" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="B181" s="1" t="s">
+      <c r="K186" s="1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="187" spans="1:26" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A187" s="9" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="188" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B188" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="C181" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="E181" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="G181" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H181" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I181" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="182" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="B182" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="G182" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H182" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J182" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="K182" s="1" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="183" spans="1:29" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A183" s="9" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="184" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="B184" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="C184" s="1" t="s">
+      <c r="C188" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D184" s="1" t="s">
+      <c r="D188" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="E184" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G184" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H184" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="M184" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="N184" s="1" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="185" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="B185" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C185" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E185" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G185" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H185" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="M185" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="N185" s="1" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="186" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="B186" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E186" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G186" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H186" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z186" s="1" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="187" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="B187" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="C187" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="E187" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G187" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H187" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="I187" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="K187" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="O187" s="1" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="188" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="B188" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>346</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>46</v>
@@ -6439,30 +6519,24 @@
         <v>47</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="I188" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="K188" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="L188" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="O188" s="1" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="189" spans="1:29" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+      <c r="M188" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="N188" s="1" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="189" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B189" s="1" t="s">
-        <v>350</v>
+        <v>319</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>351</v>
+        <v>53</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>351</v>
+        <v>49</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>46</v>
@@ -6471,27 +6545,24 @@
         <v>47</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="I189" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="K189" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="S189" s="1" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="190" spans="1:29" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+      <c r="M189" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="N189" s="1" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="190" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B190" s="1" t="s">
-        <v>357</v>
+        <v>320</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>358</v>
+        <v>57</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>358</v>
+        <v>58</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>46</v>
@@ -6502,31 +6573,19 @@
       <c r="H190" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I190" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="K190" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="L190" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="O190" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="S190" s="1" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="191" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="Z190" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="191" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B191" s="1" t="s">
-        <v>364</v>
+        <v>321</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>365</v>
+        <v>322</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>365</v>
+        <v>322</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>46</v>
@@ -6535,27 +6594,27 @@
         <v>47</v>
       </c>
       <c r="H191" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="I191" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q191" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="AC191" s="1" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="192" spans="1:29" x14ac:dyDescent="0.2">
+        <v>329</v>
+      </c>
+      <c r="K191" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="O191" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="192" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B192" s="1" t="s">
-        <v>370</v>
+        <v>343</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>371</v>
+        <v>344</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>371</v>
+        <v>344</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>46</v>
@@ -6564,30 +6623,30 @@
         <v>47</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>372</v>
+        <v>298</v>
       </c>
       <c r="K192" s="1" t="s">
-        <v>373</v>
+        <v>345</v>
       </c>
       <c r="L192" s="1" t="s">
-        <v>374</v>
+        <v>346</v>
       </c>
       <c r="O192" s="1" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="193" spans="2:26" x14ac:dyDescent="0.2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="193" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B193" s="1" t="s">
-        <v>376</v>
+        <v>348</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>377</v>
+        <v>349</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>377</v>
+        <v>349</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>46</v>
@@ -6596,30 +6655,27 @@
         <v>47</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="I193" s="1" t="s">
-        <v>378</v>
+        <v>350</v>
       </c>
       <c r="K193" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="L193" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="O193" s="1" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="194" spans="2:26" x14ac:dyDescent="0.2">
+        <v>351</v>
+      </c>
+      <c r="S193" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="194" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B194" s="1" t="s">
-        <v>384</v>
+        <v>355</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>385</v>
+        <v>356</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>385</v>
+        <v>356</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>46</v>
@@ -6628,31 +6684,62 @@
         <v>47</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>297</v>
+        <v>48</v>
       </c>
       <c r="I194" s="1" t="s">
-        <v>378</v>
+        <v>302</v>
       </c>
       <c r="K194" s="1" t="s">
-        <v>379</v>
+        <v>357</v>
       </c>
       <c r="L194" s="1" t="s">
-        <v>386</v>
+        <v>358</v>
       </c>
       <c r="O194" s="1" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="195" spans="2:26" s="9" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="196" spans="2:26" x14ac:dyDescent="0.2">
+        <v>359</v>
+      </c>
+      <c r="S194" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="195" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B195" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G195" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H195" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="I195" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q195" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="AC195" s="1" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="196" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B196" s="1" t="s">
-        <v>315</v>
+        <v>368</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>52</v>
+        <v>369</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>49</v>
+        <v>369</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>46</v>
@@ -6661,12 +6748,141 @@
         <v>47</v>
       </c>
       <c r="H196" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="I196" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="K196" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="L196" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="O196" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="197" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B197" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G197" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H197" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="I197" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="K197" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="L197" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="O197" s="1" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="198" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B198" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G198" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H198" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="I198" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="K198" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="L198" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="O198" s="1" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="199" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B199" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="E199" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G199" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H199" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="I199" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="K199" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="L199" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="O199" s="1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="200" spans="2:29" s="9" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="201" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B201" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G201" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H201" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I196" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="Z196" s="1" t="s">
+      <c r="I201" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="Z201" s="1" t="s">
         <v>51</v>
       </c>
     </row>

--- a/Luban/Config/Datas/#BattleBuffConfig.xlsx
+++ b/Luban/Config/Datas/#BattleBuffConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4317A62-AD2A-4D9A-83A4-3F509E059AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10CB835C-3BEF-4A10-9353-8F07E01C43DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView minimized="1" xWindow="3240" yWindow="3240" windowWidth="35565" windowHeight="9315" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="394">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2729,55 +2729,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>每有一个键该招式威力增加5的百分比</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleBuffChangeTempSkillDamageRateByKeyCount</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>本次交锋不会被破招</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleBuffDontBeCounter</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>本次交锋不会被被未带有↓类留劲状态的敌手破招</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>本次交锋不会被被未带有↑类留劲状态的敌手破招</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>本次交锋不会被被未带有←类留劲状态的敌手破招</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>本次交锋不会被被未带有→类留劲状态的敌手破招</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>封穴↑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9,2,10,2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2963,7 +2915,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2993,9 +2945,6 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3311,7 +3260,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:AE201"/>
+  <dimension ref="A1:AE195"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.125" style="1" bestFit="1" customWidth="1"/>
@@ -3908,7 +3857,7 @@
         <v>10131</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>184</v>
@@ -4182,7 +4131,7 @@
         <v>20031</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>188</v>
@@ -6121,7 +6070,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B161" s="2">
         <v>40551</v>
       </c>
@@ -6129,7 +6078,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B162" s="2">
         <v>40561</v>
       </c>
@@ -6137,7 +6086,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B163" s="2">
         <v>40571</v>
       </c>
@@ -6145,7 +6094,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B164" s="2">
         <v>40581</v>
       </c>
@@ -6153,7 +6102,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B165" s="2">
         <v>40591</v>
       </c>
@@ -6161,7 +6110,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B166" s="2">
         <v>40601</v>
       </c>
@@ -6169,7 +6118,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B167" s="2">
         <v>40611</v>
       </c>
@@ -6177,7 +6126,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B168" s="2">
         <v>40621</v>
       </c>
@@ -6185,7 +6134,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B169" s="2">
         <v>40631</v>
       </c>
@@ -6193,7 +6142,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B170" s="2">
         <v>40641</v>
       </c>
@@ -6201,7 +6150,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B171" s="2">
         <v>40651</v>
       </c>
@@ -6209,7 +6158,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B172" s="2">
         <v>40661</v>
       </c>
@@ -6217,7 +6166,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B173" s="2">
         <v>40671</v>
       </c>
@@ -6225,7 +6174,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B174" s="2">
         <v>40681</v>
       </c>
@@ -6233,284 +6182,293 @@
         <v>46</v>
       </c>
     </row>
-    <row r="175" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A175" s="9" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B176" s="2">
-        <v>70001</v>
-      </c>
-      <c r="C176" s="10" t="s">
-        <v>388</v>
-      </c>
-      <c r="D176" s="10" t="s">
-        <v>388</v>
-      </c>
-      <c r="E176" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="G176" s="1" t="s">
+    <row r="176" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A176" s="9" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="177" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="B177" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G177" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H177" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I177" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="178" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="B178" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G178" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H178" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J178" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H176" s="1" t="s">
+      <c r="K178" s="1" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="179" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="B179" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G179" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H179" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I179" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="180" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="B180" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="G180" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H180" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J180" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K180" s="1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="181" spans="1:29" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A181" s="9" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="182" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="B182" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G182" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H182" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I176" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="J176" s="1" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="177" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B177" s="2">
-        <v>71000</v>
-      </c>
-      <c r="C177" s="10" t="s">
-        <v>391</v>
-      </c>
-      <c r="D177" s="10" t="s">
-        <v>391</v>
-      </c>
-      <c r="E177" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="G177" s="1" t="s">
+      <c r="M182" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="N182" s="1" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="183" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="B183" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G183" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H177" s="1" t="s">
+      <c r="H183" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I177" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="J177" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="178" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B178" s="2">
-        <v>71001</v>
-      </c>
-      <c r="C178" s="10" t="s">
-        <v>394</v>
-      </c>
-      <c r="D178" s="10" t="s">
-        <v>394</v>
-      </c>
-      <c r="E178" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="G178" s="1" t="s">
+      <c r="M183" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="N183" s="1" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="184" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="B184" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G184" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H178" s="1" t="s">
+      <c r="H184" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I178" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="J178" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="179" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B179" s="2">
-        <v>71002</v>
-      </c>
-      <c r="C179" s="10" t="s">
-        <v>393</v>
-      </c>
-      <c r="D179" s="10" t="s">
-        <v>393</v>
-      </c>
-      <c r="E179" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="G179" s="1" t="s">
+      <c r="Z184" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="185" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="B185" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G185" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H179" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I179" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="J179" s="1" t="s">
+      <c r="H185" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="I185" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="K185" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="O185" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="186" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="B186" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G186" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="180" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B180" s="2">
-        <v>71003</v>
-      </c>
-      <c r="C180" s="10" t="s">
-        <v>395</v>
-      </c>
-      <c r="D180" s="10" t="s">
-        <v>395</v>
-      </c>
-      <c r="E180" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="G180" s="1" t="s">
+      <c r="H186" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="I186" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="K186" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="L186" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="O186" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="187" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="B187" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G187" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H180" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I180" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="J180" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="181" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B181" s="2">
-        <v>71004</v>
-      </c>
-      <c r="C181" s="10" t="s">
-        <v>396</v>
-      </c>
-      <c r="D181" s="10" t="s">
-        <v>396</v>
-      </c>
-      <c r="E181" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="G181" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H181" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I181" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="J181" s="1" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="182" spans="1:26" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A182" s="9" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="183" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B183" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E183" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="G183" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H183" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I183" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="184" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B184" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E184" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="G184" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H184" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J184" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="K184" s="1" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="185" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B185" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="C185" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="E185" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="G185" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H185" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I185" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="186" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B186" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="E186" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="G186" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H186" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J186" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="K186" s="1" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="187" spans="1:26" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A187" s="9" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="188" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="H187" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="I187" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="K187" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="S187" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="188" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B188" s="1" t="s">
-        <v>318</v>
+        <v>355</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>53</v>
+        <v>356</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>54</v>
+        <v>356</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>46</v>
@@ -6521,22 +6479,31 @@
       <c r="H188" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="M188" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="N188" s="1" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="189" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="I188" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="K188" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="L188" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="O188" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="S188" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="189" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B189" s="1" t="s">
-        <v>319</v>
+        <v>362</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>53</v>
+        <v>363</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>49</v>
+        <v>363</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>46</v>
@@ -6545,24 +6512,27 @@
         <v>47</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="M189" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="N189" s="1" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="190" spans="1:26" x14ac:dyDescent="0.2">
+        <v>295</v>
+      </c>
+      <c r="I189" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q189" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="AC189" s="1" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="190" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B190" s="1" t="s">
-        <v>320</v>
+        <v>368</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>57</v>
+        <v>369</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>58</v>
+        <v>369</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>46</v>
@@ -6571,21 +6541,30 @@
         <v>47</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z190" s="1" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="191" spans="1:26" x14ac:dyDescent="0.2">
+        <v>295</v>
+      </c>
+      <c r="I190" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="K190" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="L190" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="O190" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="191" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B191" s="1" t="s">
-        <v>321</v>
+        <v>374</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>322</v>
+        <v>375</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>322</v>
+        <v>375</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>46</v>
@@ -6597,24 +6576,27 @@
         <v>295</v>
       </c>
       <c r="I191" s="1" t="s">
-        <v>329</v>
+        <v>376</v>
       </c>
       <c r="K191" s="1" t="s">
-        <v>330</v>
+        <v>377</v>
+      </c>
+      <c r="L191" s="1" t="s">
+        <v>378</v>
       </c>
       <c r="O191" s="1" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="192" spans="1:26" x14ac:dyDescent="0.2">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="192" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B192" s="1" t="s">
-        <v>343</v>
+        <v>382</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>344</v>
+        <v>383</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>344</v>
+        <v>383</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>46</v>
@@ -6626,27 +6608,27 @@
         <v>295</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>298</v>
+        <v>376</v>
       </c>
       <c r="K192" s="1" t="s">
-        <v>345</v>
+        <v>377</v>
       </c>
       <c r="L192" s="1" t="s">
-        <v>346</v>
+        <v>384</v>
       </c>
       <c r="O192" s="1" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="193" spans="2:29" x14ac:dyDescent="0.2">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="193" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B193" s="1" t="s">
-        <v>348</v>
+        <v>390</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>349</v>
+        <v>391</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>349</v>
+        <v>391</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>46</v>
@@ -6658,59 +6640,28 @@
         <v>295</v>
       </c>
       <c r="I193" s="1" t="s">
-        <v>350</v>
+        <v>298</v>
       </c>
       <c r="K193" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="S193" s="1" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="194" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B194" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="D194" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="E194" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G194" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H194" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I194" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="K194" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="L194" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="O194" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="S194" s="1" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="195" spans="2:29" x14ac:dyDescent="0.2">
+        <v>345</v>
+      </c>
+      <c r="L193" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="O193" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="194" spans="2:26" s="9" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="195" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B195" s="1" t="s">
-        <v>362</v>
+        <v>313</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>363</v>
+        <v>52</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>363</v>
+        <v>49</v>
       </c>
       <c r="E195" s="1" t="s">
         <v>46</v>
@@ -6719,170 +6670,12 @@
         <v>47</v>
       </c>
       <c r="H195" s="1" t="s">
-        <v>295</v>
+        <v>48</v>
       </c>
       <c r="I195" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q195" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="AC195" s="1" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="196" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B196" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="C196" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="D196" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="E196" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G196" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H196" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="I196" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="K196" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="L196" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="O196" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="197" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B197" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="C197" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="D197" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="E197" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G197" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H197" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="I197" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="K197" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="L197" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="O197" s="1" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="198" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B198" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="C198" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D198" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="E198" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G198" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H198" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="I198" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="K198" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="L198" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="O198" s="1" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="199" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B199" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="C199" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="D199" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="E199" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G199" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H199" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="I199" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="K199" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="L199" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="O199" s="1" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="200" spans="2:29" s="9" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="201" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B201" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="C201" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D201" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E201" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G201" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H201" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I201" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="Z201" s="1" t="s">
+      <c r="Z195" s="1" t="s">
         <v>51</v>
       </c>
     </row>

--- a/Luban/Config/Datas/#BattleBuffConfig.xlsx
+++ b/Luban/Config/Datas/#BattleBuffConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77E37C43-BEA1-4DC7-BDBC-532E04B08E2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B69D148-0DF2-4452-83FE-7E114C6DA652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -95,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="449">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -340,10 +340,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>BattleBuffShield</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2391,10 +2387,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>BattleBuffArmor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>BattleBuffArmorDelay</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2951,6 +2943,38 @@
   </si>
   <si>
     <t>封锁两个键直到回合结束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下一次术杀式的基础威力不会低于140%技（巧来方计状态）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>74041</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleBuff74041</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,1,1.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>74046</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下一次行动中恢复刚炁时获得等量玄炁，恢复玄炁时获得等量刚炁（玉摄念状态）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleBuff74046</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动后减少一层(默认两层)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3479,13 +3503,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:AH256"/>
+  <dimension ref="A1:AH258"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.75" style="1" customWidth="1"/>
     <col min="3" max="3" width="31.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="47.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="158.375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="53.125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="25.875" style="1" customWidth="1"/>
     <col min="7" max="7" width="13.375" style="1" bestFit="1" customWidth="1"/>
@@ -3536,7 +3560,7 @@
         <v>44</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>37</v>
@@ -3548,25 +3572,25 @@
         <v>28</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>18</v>
@@ -3575,13 +3599,13 @@
         <v>20</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="U1" s="12" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>56</v>
@@ -3608,19 +3632,19 @@
         <v>13</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AE1" s="1" t="s">
         <v>22</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.2">
@@ -3655,7 +3679,7 @@
         <v>26</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>26</v>
@@ -3741,7 +3765,7 @@
         <v>45</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>38</v>
@@ -3753,13 +3777,13 @@
         <v>27</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>41</v>
@@ -3768,7 +3792,7 @@
         <v>39</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="Q3" s="1" t="s">
         <v>19</v>
@@ -3777,13 +3801,13 @@
         <v>21</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="T3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="U3" s="12" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="V3" s="1" t="s">
         <v>55</v>
@@ -3810,7 +3834,7 @@
         <v>24</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AE3" s="1" t="s">
         <v>23</v>
@@ -3819,10 +3843,10 @@
         <v>36</v>
       </c>
       <c r="AG3" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AH3" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.2">
@@ -3830,22 +3854,22 @@
         <v>10011</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AH5" s="1" t="s">
         <v>48</v>
@@ -3856,19 +3880,19 @@
         <v>10021</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>50</v>
@@ -3882,19 +3906,19 @@
         <v>10031</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>50</v>
@@ -3908,22 +3932,22 @@
         <v>10041</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AH8" s="1" t="s">
         <v>48</v>
@@ -3934,22 +3958,22 @@
         <v>10051</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AH9" s="1" t="s">
         <v>48</v>
@@ -3960,22 +3984,22 @@
         <v>10061</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AH10" s="1" t="s">
         <v>48</v>
@@ -3986,22 +4010,22 @@
         <v>10071</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AH11" s="1" t="s">
         <v>48</v>
@@ -4012,22 +4036,22 @@
         <v>10081</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AH12" s="1" t="s">
         <v>48</v>
@@ -4038,22 +4062,22 @@
         <v>10091</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AH13" s="1" t="s">
         <v>48</v>
@@ -4064,22 +4088,22 @@
         <v>10101</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AH14" s="1" t="s">
         <v>48</v>
@@ -4090,22 +4114,22 @@
         <v>10111</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AH15" s="1" t="s">
         <v>48</v>
@@ -4116,10 +4140,10 @@
         <v>10121</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>46</v>
@@ -4131,7 +4155,7 @@
         <v>48</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AH16" s="1" t="s">
         <v>48</v>
@@ -4142,10 +4166,10 @@
         <v>10131</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>46</v>
@@ -4165,22 +4189,22 @@
         <v>10141</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H18" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="I18" s="1" t="s">
         <v>292</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>293</v>
       </c>
       <c r="AH18" s="1" t="s">
         <v>48</v>
@@ -4191,10 +4215,10 @@
         <v>10151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>46</v>
@@ -4206,7 +4230,7 @@
         <v>48</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AH19" s="1" t="s">
         <v>48</v>
@@ -4217,10 +4241,10 @@
         <v>10161</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>46</v>
@@ -4232,7 +4256,7 @@
         <v>48</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AH20" s="1" t="s">
         <v>48</v>
@@ -4243,10 +4267,10 @@
         <v>10171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>46</v>
@@ -4258,7 +4282,7 @@
         <v>48</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AH21" s="1" t="s">
         <v>48</v>
@@ -4269,22 +4293,22 @@
         <v>10181</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AH22" s="1" t="s">
         <v>48</v>
@@ -4295,10 +4319,10 @@
         <v>10191</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>46</v>
@@ -4310,7 +4334,7 @@
         <v>48</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AH23" s="1" t="s">
         <v>48</v>
@@ -4321,10 +4345,10 @@
         <v>10201</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>46</v>
@@ -4336,7 +4360,7 @@
         <v>48</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AH24" s="1" t="s">
         <v>48</v>
@@ -4347,22 +4371,22 @@
         <v>10211</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AH25" s="1" t="s">
         <v>48</v>
@@ -4373,22 +4397,22 @@
         <v>10221</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AH26" s="1" t="s">
         <v>48</v>
@@ -4400,22 +4424,22 @@
         <v>20011</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H28" s="3">
         <v>10</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AH28" s="1" t="s">
         <v>48</v>
@@ -4426,22 +4450,22 @@
         <v>20021</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H29" s="3">
         <v>8</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AH29" s="1" t="s">
         <v>48</v>
@@ -4452,10 +4476,10 @@
         <v>20031</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>46</v>
@@ -4467,7 +4491,7 @@
         <v>1</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AH30" s="1" t="s">
         <v>48</v>
@@ -4478,10 +4502,10 @@
         <v>20041</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>46</v>
@@ -4493,7 +4517,7 @@
         <v>1</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AH31" s="1" t="s">
         <v>48</v>
@@ -4504,10 +4528,10 @@
         <v>20051</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>46</v>
@@ -4519,7 +4543,7 @@
         <v>1</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AH32" s="1" t="s">
         <v>48</v>
@@ -4530,10 +4554,10 @@
         <v>20061</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>46</v>
@@ -4545,7 +4569,7 @@
         <v>1</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AH33" s="1" t="s">
         <v>48</v>
@@ -4556,10 +4580,10 @@
         <v>20071</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>46</v>
@@ -4571,7 +4595,7 @@
         <v>1</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AH34" s="1" t="s">
         <v>48</v>
@@ -4582,10 +4606,10 @@
         <v>20081</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>46</v>
@@ -4597,7 +4621,7 @@
         <v>1</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AH35" s="1" t="s">
         <v>48</v>
@@ -4608,22 +4632,22 @@
         <v>20091</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H36" s="3">
         <v>5</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AH36" s="1" t="s">
         <v>48</v>
@@ -4634,22 +4658,22 @@
         <v>20101</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H37" s="3">
         <v>5</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AH37" s="1" t="s">
         <v>48</v>
@@ -4660,22 +4684,22 @@
         <v>20111</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H38" s="3">
         <v>5</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AH38" s="1" t="s">
         <v>48</v>
@@ -4686,22 +4710,22 @@
         <v>20121</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H39" s="3">
         <v>5</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AH39" s="1" t="s">
         <v>48</v>
@@ -4712,22 +4736,22 @@
         <v>20131</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H40" s="3">
         <v>5</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AH40" s="1" t="s">
         <v>48</v>
@@ -4738,22 +4762,22 @@
         <v>20141</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H41" s="3">
         <v>5</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AH41" s="1" t="s">
         <v>48</v>
@@ -4764,10 +4788,10 @@
         <v>20151</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>46</v>
@@ -4779,7 +4803,7 @@
         <v>1</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AH42" s="1" t="s">
         <v>48</v>
@@ -4790,10 +4814,10 @@
         <v>20161</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>46</v>
@@ -4805,7 +4829,7 @@
         <v>1</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AH43" s="1" t="s">
         <v>48</v>
@@ -4816,10 +4840,10 @@
         <v>20171</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>46</v>
@@ -4842,10 +4866,10 @@
         <v>20181</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>46</v>
@@ -4857,7 +4881,7 @@
         <v>1</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AH45" s="1" t="s">
         <v>48</v>
@@ -4868,10 +4892,10 @@
         <v>20191</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>46</v>
@@ -4883,7 +4907,7 @@
         <v>1</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AH46" s="1" t="s">
         <v>48</v>
@@ -4894,10 +4918,10 @@
         <v>20201</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>46</v>
@@ -4909,7 +4933,7 @@
         <v>1</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AH47" s="1" t="s">
         <v>48</v>
@@ -4920,10 +4944,10 @@
         <v>20211</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>46</v>
@@ -4935,7 +4959,7 @@
         <v>1</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AH48" s="1" t="s">
         <v>48</v>
@@ -4946,16 +4970,16 @@
         <v>20221</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H49" s="3">
         <v>10</v>
@@ -4969,16 +4993,16 @@
         <v>20231</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H50" s="3">
         <v>-1</v>
@@ -4992,22 +5016,22 @@
         <v>20241</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H51" s="3">
         <v>1</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AH51" s="1" t="s">
         <v>48</v>
@@ -5018,22 +5042,22 @@
         <v>20251</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H52" s="3">
         <v>1</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AH52" s="1" t="s">
         <v>48</v>
@@ -5044,22 +5068,22 @@
         <v>20261</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H53" s="3">
         <v>1</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AH53" s="1" t="s">
         <v>48</v>
@@ -5070,22 +5094,22 @@
         <v>20271</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H54" s="3">
         <v>1</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AH54" s="1" t="s">
         <v>48</v>
@@ -5096,10 +5120,10 @@
         <v>20281</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>46</v>
@@ -5111,7 +5135,7 @@
         <v>1</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AH55" s="1" t="s">
         <v>48</v>
@@ -5122,22 +5146,22 @@
         <v>20291</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H56" s="3">
         <v>-1</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AH56" s="1" t="s">
         <v>48</v>
@@ -5148,22 +5172,22 @@
         <v>20301</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H57" s="3">
         <v>5</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AH57" s="1" t="s">
         <v>48</v>
@@ -5174,22 +5198,22 @@
         <v>20311</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H58" s="3">
         <v>5</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AH58" s="1" t="s">
         <v>48</v>
@@ -5200,10 +5224,10 @@
         <v>20321</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>46</v>
@@ -5215,7 +5239,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AH59" s="1" t="s">
         <v>48</v>
@@ -5226,10 +5250,10 @@
         <v>20331</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>46</v>
@@ -5241,7 +5265,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AH60" s="1" t="s">
         <v>48</v>
@@ -5252,16 +5276,16 @@
         <v>20341</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H61" s="3">
         <v>10</v>
@@ -5275,22 +5299,22 @@
         <v>20351</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H62" s="3">
         <v>-1</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AH62" s="1" t="s">
         <v>48</v>
@@ -5302,10 +5326,10 @@
         <v>30011</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>46</v>
@@ -5319,10 +5343,10 @@
         <v>30021</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>46</v>
@@ -5336,10 +5360,10 @@
         <v>30031</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>46</v>
@@ -5353,10 +5377,10 @@
         <v>30041</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>46</v>
@@ -5370,10 +5394,10 @@
         <v>30051</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>46</v>
@@ -5387,10 +5411,10 @@
         <v>30061</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>46</v>
@@ -5404,10 +5428,10 @@
         <v>30071</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>46</v>
@@ -5421,10 +5445,10 @@
         <v>30081</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>46</v>
@@ -5438,10 +5462,10 @@
         <v>30091</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>46</v>
@@ -5455,10 +5479,10 @@
         <v>30101</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>46</v>
@@ -5472,10 +5496,10 @@
         <v>30111</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>46</v>
@@ -5489,10 +5513,10 @@
         <v>30121</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>46</v>
@@ -5506,10 +5530,10 @@
         <v>30131</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>46</v>
@@ -5523,10 +5547,10 @@
         <v>30141</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>46</v>
@@ -5540,10 +5564,10 @@
         <v>30151</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>46</v>
@@ -5557,10 +5581,10 @@
         <v>30161</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>46</v>
@@ -5574,10 +5598,10 @@
         <v>30171</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>46</v>
@@ -5591,10 +5615,10 @@
         <v>30181</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>46</v>
@@ -5608,10 +5632,10 @@
         <v>30191</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>46</v>
@@ -5625,10 +5649,10 @@
         <v>30201</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>46</v>
@@ -5642,10 +5666,10 @@
         <v>30211</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>46</v>
@@ -5659,10 +5683,10 @@
         <v>30221</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>46</v>
@@ -5676,10 +5700,10 @@
         <v>30231</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>46</v>
@@ -5693,10 +5717,10 @@
         <v>30241</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>46</v>
@@ -5710,10 +5734,10 @@
         <v>30251</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>46</v>
@@ -5727,10 +5751,10 @@
         <v>30261</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>46</v>
@@ -5744,10 +5768,10 @@
         <v>30271</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>46</v>
@@ -5761,10 +5785,10 @@
         <v>30281</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>46</v>
@@ -5778,10 +5802,10 @@
         <v>30291</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>46</v>
@@ -5795,10 +5819,10 @@
         <v>30301</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>46</v>
@@ -5812,7 +5836,7 @@
         <v>30311</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" s="1" t="s">
@@ -5827,10 +5851,10 @@
         <v>30321</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>46</v>
@@ -5844,10 +5868,10 @@
         <v>30331</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>46</v>
@@ -5861,10 +5885,10 @@
         <v>30341</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>46</v>
@@ -5878,10 +5902,10 @@
         <v>30351</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>46</v>
@@ -5895,10 +5919,10 @@
         <v>30361</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>46</v>
@@ -5912,10 +5936,10 @@
         <v>30371</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>46</v>
@@ -5929,10 +5953,10 @@
         <v>30381</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>46</v>
@@ -5946,10 +5970,10 @@
         <v>30391</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>46</v>
@@ -5963,10 +5987,10 @@
         <v>30401</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>46</v>
@@ -5980,10 +6004,10 @@
         <v>30411</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>46</v>
@@ -5997,19 +6021,19 @@
         <v>30421</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G105" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H105" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="H105" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="AH105" s="1" t="s">
         <v>48</v>
@@ -6021,10 +6045,10 @@
         <v>40011</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>46</v>
@@ -6035,10 +6059,10 @@
         <v>40021</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D108" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>46</v>
@@ -6049,10 +6073,10 @@
         <v>40031</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>46</v>
@@ -6063,10 +6087,10 @@
         <v>40041</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>46</v>
@@ -6077,10 +6101,10 @@
         <v>40051</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>46</v>
@@ -6091,10 +6115,10 @@
         <v>40061</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>46</v>
@@ -6105,10 +6129,10 @@
         <v>40071</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>46</v>
@@ -6119,10 +6143,10 @@
         <v>40081</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>46</v>
@@ -6133,10 +6157,10 @@
         <v>40091</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>46</v>
@@ -6147,10 +6171,10 @@
         <v>40101</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>46</v>
@@ -6161,10 +6185,10 @@
         <v>40111</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>46</v>
@@ -6175,10 +6199,10 @@
         <v>40121</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>46</v>
@@ -6189,10 +6213,10 @@
         <v>40131</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>46</v>
@@ -6203,10 +6227,10 @@
         <v>40141</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>46</v>
@@ -6217,10 +6241,10 @@
         <v>40151</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>46</v>
@@ -6231,10 +6255,10 @@
         <v>40161</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>46</v>
@@ -6245,10 +6269,10 @@
         <v>40171</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>46</v>
@@ -6259,10 +6283,10 @@
         <v>40181</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>46</v>
@@ -6273,10 +6297,10 @@
         <v>40191</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>46</v>
@@ -6287,10 +6311,10 @@
         <v>40201</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>46</v>
@@ -6301,10 +6325,10 @@
         <v>40211</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>46</v>
@@ -6315,10 +6339,10 @@
         <v>40221</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>46</v>
@@ -6329,10 +6353,10 @@
         <v>40231</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>46</v>
@@ -6343,10 +6367,10 @@
         <v>40241</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>46</v>
@@ -6357,10 +6381,10 @@
         <v>40251</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>46</v>
@@ -6371,7 +6395,7 @@
         <v>40261</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>46</v>
@@ -6382,7 +6406,7 @@
         <v>40271</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>46</v>
@@ -6393,7 +6417,7 @@
         <v>40281</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>46</v>
@@ -6404,7 +6428,7 @@
         <v>40291</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>46</v>
@@ -6415,7 +6439,7 @@
         <v>40301</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>46</v>
@@ -6426,7 +6450,7 @@
         <v>40311</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>46</v>
@@ -6730,7 +6754,7 @@
     </row>
     <row r="175" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A175" s="10" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.2">
@@ -6738,13 +6762,13 @@
         <v>72008</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G176" s="1" t="s">
         <v>47</v>
@@ -6756,10 +6780,10 @@
         <v>50</v>
       </c>
       <c r="K176" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="L176" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="177" spans="1:28" x14ac:dyDescent="0.2">
@@ -6767,45 +6791,45 @@
         <v>72053</v>
       </c>
       <c r="C177" s="11" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="G177" s="1" t="s">
         <v>47</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L177" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="178" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B178" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="G178" s="1" t="s">
         <v>47</v>
       </c>
       <c r="H178" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I178" s="1" t="s">
         <v>50</v>
@@ -6814,227 +6838,207 @@
         <v>47</v>
       </c>
       <c r="L178" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="179" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B179" s="1" t="s">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="G179" s="1" t="s">
         <v>47</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>66</v>
+        <v>292</v>
+      </c>
+      <c r="K179" s="1" t="s">
+        <v>444</v>
       </c>
       <c r="L179" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="180" spans="1:28" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A180" s="9" t="s">
-        <v>299</v>
+        <v>439</v>
+      </c>
+    </row>
+    <row r="180" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B180" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="G180" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H180" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="I180" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="L180" s="1" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="181" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B181" s="1" t="s">
-        <v>309</v>
+        <v>427</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>60</v>
+        <v>428</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>59</v>
+        <v>421</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>61</v>
+        <v>420</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="H181" s="1" t="s">
-        <v>63</v>
+        <v>289</v>
       </c>
       <c r="I181" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="182" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B182" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D182" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E182" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="G182" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H182" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="K182" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="L182" s="1" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="183" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B183" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="E183" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="G183" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H183" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I183" s="1" t="s">
-        <v>50</v>
+      <c r="L181" s="1" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="183" spans="1:28" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A183" s="9" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="184" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B184" s="1" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>301</v>
+        <v>60</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>301</v>
+        <v>59</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>303</v>
+        <v>46</v>
       </c>
       <c r="G184" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H184" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="H184" s="1" t="s">
+      <c r="I184" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="185" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B185" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C185" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="K184" s="1" t="s">
+      <c r="D185" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G185" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H185" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K185" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="L184" s="1" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="185" spans="1:28" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A185" s="9" t="s">
-        <v>307</v>
+      <c r="L185" s="1" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="186" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B186" s="1" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>53</v>
+        <v>299</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>54</v>
+        <v>299</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="H186" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="N186" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="O186" s="1" t="s">
-        <v>330</v>
+        <v>62</v>
+      </c>
+      <c r="I186" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="187" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B187" s="1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>53</v>
+        <v>300</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>49</v>
+        <v>300</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>46</v>
+        <v>301</v>
       </c>
       <c r="G187" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H187" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K187" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H187" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="N187" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="O187" s="1" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="188" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B188" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E188" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G188" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H188" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB188" s="1" t="s">
-        <v>328</v>
+      <c r="L187" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="188" spans="1:28" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A188" s="9" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="189" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B189" s="1" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>317</v>
+        <v>53</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>317</v>
+        <v>54</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>46</v>
@@ -7043,27 +7047,24 @@
         <v>47</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="I189" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="L189" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="P189" s="1" t="s">
-        <v>333</v>
+        <v>48</v>
+      </c>
+      <c r="N189" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="O189" s="1" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="190" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B190" s="1" t="s">
-        <v>338</v>
+        <v>312</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>339</v>
+        <v>53</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>339</v>
+        <v>49</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>46</v>
@@ -7072,30 +7073,24 @@
         <v>47</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="I190" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="L190" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="M190" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="P190" s="1" t="s">
-        <v>342</v>
+        <v>48</v>
+      </c>
+      <c r="N190" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="O190" s="1" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="191" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B191" s="1" t="s">
-        <v>343</v>
+        <v>313</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>344</v>
+        <v>57</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>344</v>
+        <v>58</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>46</v>
@@ -7104,27 +7099,21 @@
         <v>47</v>
       </c>
       <c r="H191" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="I191" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="L191" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="T191" s="1" t="s">
-        <v>347</v>
+        <v>48</v>
+      </c>
+      <c r="AB191" s="1" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="192" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B192" s="1" t="s">
-        <v>350</v>
+        <v>314</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>351</v>
+        <v>315</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>351</v>
+        <v>315</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>46</v>
@@ -7133,33 +7122,27 @@
         <v>47</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>48</v>
+        <v>289</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>297</v>
+        <v>322</v>
       </c>
       <c r="L192" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="M192" s="1" t="s">
-        <v>353</v>
+        <v>323</v>
       </c>
       <c r="P192" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="T192" s="1" t="s">
-        <v>347</v>
+        <v>331</v>
       </c>
     </row>
     <row r="193" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B193" s="1" t="s">
-        <v>357</v>
+        <v>336</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>358</v>
+        <v>337</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>358</v>
+        <v>337</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>46</v>
@@ -7168,27 +7151,30 @@
         <v>47</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I193" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="R193" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="AE193" s="1" t="s">
-        <v>360</v>
+        <v>292</v>
+      </c>
+      <c r="L193" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="M193" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="P193" s="1" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="194" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B194" s="1" t="s">
-        <v>363</v>
+        <v>341</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>364</v>
+        <v>342</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>364</v>
+        <v>342</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>46</v>
@@ -7197,30 +7183,27 @@
         <v>47</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I194" s="1" t="s">
-        <v>365</v>
+        <v>343</v>
       </c>
       <c r="L194" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="M194" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="P194" s="1" t="s">
-        <v>368</v>
+        <v>344</v>
+      </c>
+      <c r="T194" s="1" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="195" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B195" s="1" t="s">
-        <v>369</v>
+        <v>348</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>370</v>
+        <v>349</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>370</v>
+        <v>349</v>
       </c>
       <c r="E195" s="1" t="s">
         <v>46</v>
@@ -7229,30 +7212,33 @@
         <v>47</v>
       </c>
       <c r="H195" s="1" t="s">
-        <v>290</v>
+        <v>48</v>
       </c>
       <c r="I195" s="1" t="s">
-        <v>371</v>
+        <v>296</v>
       </c>
       <c r="L195" s="1" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="M195" s="1" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="P195" s="1" t="s">
-        <v>374</v>
+        <v>352</v>
+      </c>
+      <c r="T195" s="1" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="196" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B196" s="1" t="s">
-        <v>377</v>
+        <v>355</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>378</v>
+        <v>356</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>378</v>
+        <v>356</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>46</v>
@@ -7261,30 +7247,30 @@
         <v>47</v>
       </c>
       <c r="H196" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I196" s="1" t="s">
-        <v>371</v>
+        <v>65</v>
       </c>
       <c r="L196" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="M196" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="P196" s="1" t="s">
-        <v>380</v>
+        <v>422</v>
+      </c>
+      <c r="R196" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="AE196" s="1" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="197" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B197" s="1" t="s">
-        <v>383</v>
+        <v>361</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>384</v>
+        <v>362</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>384</v>
+        <v>362</v>
       </c>
       <c r="E197" s="1" t="s">
         <v>46</v>
@@ -7293,30 +7279,30 @@
         <v>47</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I197" s="1" t="s">
-        <v>293</v>
+        <v>363</v>
       </c>
       <c r="L197" s="1" t="s">
-        <v>340</v>
+        <v>364</v>
       </c>
       <c r="M197" s="1" t="s">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="P197" s="1" t="s">
-        <v>386</v>
+        <v>366</v>
       </c>
     </row>
     <row r="198" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B198" s="1" t="s">
-        <v>399</v>
+        <v>367</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>400</v>
+        <v>368</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>400</v>
+        <v>368</v>
       </c>
       <c r="E198" s="1" t="s">
         <v>46</v>
@@ -7325,30 +7311,30 @@
         <v>47</v>
       </c>
       <c r="H198" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I198" s="1" t="s">
-        <v>401</v>
+        <v>369</v>
       </c>
       <c r="L198" s="1" t="s">
-        <v>402</v>
+        <v>370</v>
       </c>
       <c r="M198" s="1" t="s">
-        <v>403</v>
+        <v>371</v>
       </c>
       <c r="P198" s="1" t="s">
-        <v>404</v>
+        <v>372</v>
       </c>
     </row>
     <row r="199" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B199" s="1" t="s">
-        <v>405</v>
+        <v>375</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>406</v>
+        <v>376</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>406</v>
+        <v>376</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>46</v>
@@ -7357,27 +7343,30 @@
         <v>47</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I199" s="1" t="s">
-        <v>66</v>
+        <v>369</v>
       </c>
       <c r="L199" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="R199" s="1" t="s">
-        <v>408</v>
+        <v>370</v>
+      </c>
+      <c r="M199" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="P199" s="1" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="200" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B200" s="1" t="s">
-        <v>411</v>
+        <v>381</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>412</v>
+        <v>382</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>412</v>
+        <v>382</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>46</v>
@@ -7386,27 +7375,30 @@
         <v>47</v>
       </c>
       <c r="H200" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I200" s="1" t="s">
-        <v>413</v>
+        <v>292</v>
       </c>
       <c r="L200" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="U200" s="12" t="s">
-        <v>415</v>
+        <v>338</v>
+      </c>
+      <c r="M200" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="P200" s="1" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="201" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B201" s="1" t="s">
-        <v>420</v>
+        <v>397</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>431</v>
+        <v>398</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>431</v>
+        <v>398</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>46</v>
@@ -7415,33 +7407,30 @@
         <v>47</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I201" s="1" t="s">
-        <v>66</v>
+        <v>399</v>
       </c>
       <c r="L201" s="1" t="s">
-        <v>424</v>
+        <v>400</v>
       </c>
       <c r="M201" s="1" t="s">
-        <v>425</v>
+        <v>401</v>
       </c>
       <c r="P201" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="U201" s="12" t="s">
-        <v>415</v>
+        <v>402</v>
       </c>
     </row>
     <row r="202" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B202" s="1" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>432</v>
+        <v>404</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>432</v>
+        <v>404</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>46</v>
@@ -7450,30 +7439,27 @@
         <v>47</v>
       </c>
       <c r="H202" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I202" s="1" t="s">
-        <v>365</v>
+        <v>65</v>
       </c>
       <c r="L202" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="M202" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="P202" s="1" t="s">
-        <v>427</v>
+        <v>405</v>
+      </c>
+      <c r="R202" s="1" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="203" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B203" s="1" t="s">
-        <v>433</v>
+        <v>409</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>46</v>
@@ -7482,28 +7468,94 @@
         <v>47</v>
       </c>
       <c r="H203" s="1" t="s">
-        <v>48</v>
+        <v>289</v>
       </c>
       <c r="I203" s="1" t="s">
-        <v>435</v>
+        <v>411</v>
       </c>
       <c r="L203" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="S203" s="1" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="205" spans="2:31" s="9" customFormat="1" x14ac:dyDescent="0.2"/>
+        <v>412</v>
+      </c>
+      <c r="U203" s="12" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="204" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="B204" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G204" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H204" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="I204" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L204" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="M204" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="P204" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="U204" s="12" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="205" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="B205" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G205" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H205" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="I205" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="L205" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="M205" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="P205" s="1" t="s">
+        <v>425</v>
+      </c>
+    </row>
     <row r="206" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B206" s="1" t="s">
-        <v>308</v>
+        <v>431</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>52</v>
+        <v>432</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>49</v>
+        <v>432</v>
       </c>
       <c r="E206" s="1" t="s">
         <v>46</v>
@@ -7515,14 +7567,44 @@
         <v>48</v>
       </c>
       <c r="I206" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="L206" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="S206" s="1" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="207" spans="2:31" s="9" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="208" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="B208" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="AB206" s="1" t="s">
+      <c r="C208" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D208" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G208" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H208" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I208" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="AB208" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="256" spans="21:21" x14ac:dyDescent="0.2">
-      <c r="U256" s="13"/>
+    <row r="258" spans="21:21" x14ac:dyDescent="0.2">
+      <c r="U258" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Luban/Config/Datas/#BattleBuffConfig.xlsx
+++ b/Luban/Config/Datas/#BattleBuffConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9AB3757-9AA7-487C-BD29-0CF59D0341E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36D700B-3CE5-4DF3-944F-F5CF5E0C9F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>

--- a/Luban/Config/Datas/#BattleBuffConfig.xlsx
+++ b/Luban/Config/Datas/#BattleBuffConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36D700B-3CE5-4DF3-944F-F5CF5E0C9F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8DFA460-9E75-4DDA-9CEE-2E5B66416EBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -95,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1201" uniqueCount="529">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3266,6 +3266,34 @@
   </si>
   <si>
     <t>BattleBuff20321</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90019</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>失重效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无法通过状态、招式、心法效果获得键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90020</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>满欲敌手状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一次移除了超过4层的妖毒状态或妖毒侵蚀状态则在本回合获得1次行动次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleBuff90020</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3837,7 +3865,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:N206"/>
+  <dimension ref="A1:N208"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.125" style="1" bestFit="1" customWidth="1"/>
@@ -8703,30 +8731,76 @@
         <v>362</v>
       </c>
     </row>
-    <row r="205" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="205" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B205" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G205" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H205" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
     <row r="206" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B206" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="F206" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G206" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H206" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="207" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="208" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B208" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C206" s="1" t="s">
+      <c r="C208" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D206" s="1" t="s">
+      <c r="D208" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E206" s="1" t="s">
+      <c r="E208" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="F206" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G206" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H206" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L206" s="1" t="s">
+      <c r="F208" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G208" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H208" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L208" s="1" t="s">
         <v>224</v>
       </c>
     </row>

--- a/Luban/Config/Datas/#BattleBuffConfig.xlsx
+++ b/Luban/Config/Datas/#BattleBuffConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8DFA460-9E75-4DDA-9CEE-2E5B66416EBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{555D9B43-B156-4669-9BF1-3B4A828E0B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -95,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1201" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1201" uniqueCount="530">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3294,6 +3294,10 @@
   </si>
   <si>
     <t>BattleBuff90020</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleBuff80001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8142,7 +8146,7 @@
         <v>28</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>20</v>
+        <v>529</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>30</v>

--- a/Luban/Config/Datas/#BattleBuffConfig.xlsx
+++ b/Luban/Config/Datas/#BattleBuffConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{555D9B43-B156-4669-9BF1-3B4A828E0B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C789694F-CD1D-467D-8301-9DAC763E7319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>

--- a/Luban/Config/Datas/#BattleBuffConfig.xlsx
+++ b/Luban/Config/Datas/#BattleBuffConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E50BB52C-098B-4999-A720-1E22AF321537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8517EEAE-0CD4-4074-9C69-6F3076C9EAC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -95,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1193" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="531">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3283,6 +3283,26 @@
   </si>
   <si>
     <t>死楔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>73092</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本次战斗刚炁的自然恢复不会低于25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleBuff73092</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3854,7 +3874,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:N207"/>
+  <dimension ref="A1:N208"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.125" style="1" bestFit="1" customWidth="1"/>
@@ -8027,16 +8047,16 @@
     </row>
     <row r="179" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B179" s="1" t="s">
-        <v>308</v>
+        <v>527</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>306</v>
+        <v>528</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>306</v>
+        <v>528</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>309</v>
+        <v>529</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>28</v>
@@ -8048,27 +8068,24 @@
         <v>207</v>
       </c>
       <c r="K179" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="L179" s="1" t="s">
-        <v>210</v>
+        <v>471</v>
       </c>
       <c r="M179" s="1" t="s">
-        <v>304</v>
+        <v>530</v>
       </c>
     </row>
     <row r="180" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B180" s="1" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>28</v>
@@ -8079,25 +8096,28 @@
       <c r="H180" s="1" t="s">
         <v>207</v>
       </c>
+      <c r="K180" s="1" t="s">
+        <v>310</v>
+      </c>
       <c r="L180" s="1" t="s">
         <v>210</v>
       </c>
       <c r="M180" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
     </row>
     <row r="181" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B181" s="1" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>28</v>
@@ -8109,55 +8129,61 @@
         <v>207</v>
       </c>
       <c r="L181" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="M181" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="182" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B182" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G182" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H182" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="K182" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="L182" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M181" s="1" t="s">
+      <c r="M182" s="1" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="183" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A183" s="9" t="s">
+    <row r="184" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A184" s="9" t="s">
         <v>215</v>
-      </c>
-    </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B184" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E184" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="F184" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G184" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H184" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L184" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="185" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B185" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>36</v>
+        <v>524</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>28</v>
@@ -8168,25 +8194,22 @@
       <c r="H185" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K185" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M185" s="1" t="s">
-        <v>230</v>
+      <c r="L185" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="186" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B186" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>216</v>
+        <v>30</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>216</v>
+        <v>31</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>28</v>
@@ -8197,22 +8220,25 @@
       <c r="H186" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L186" s="1" t="s">
-        <v>24</v>
+      <c r="K186" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M186" s="1" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="187" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B187" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>218</v>
+        <v>20</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>28</v>
@@ -8223,59 +8249,56 @@
       <c r="H187" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K187" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M187" s="1" t="s">
+      <c r="L187" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="188" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B188" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G188" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H188" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K188" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M188" s="1" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="188" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A188" s="9" t="s">
+    <row r="189" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A189" s="9" t="s">
         <v>222</v>
-      </c>
-    </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B189" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C189" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="D189" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="F189" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G189" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H189" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="L189" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="M189" s="1" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="190" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B190" s="1" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>28</v>
@@ -8286,28 +8309,25 @@
       <c r="H190" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="K190" s="1" t="s">
-        <v>491</v>
-      </c>
       <c r="L190" s="1" t="s">
-        <v>210</v>
+        <v>493</v>
       </c>
       <c r="M190" s="1" t="s">
-        <v>235</v>
+        <v>494</v>
       </c>
     </row>
     <row r="191" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B191" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>28</v>
@@ -8318,25 +8338,28 @@
       <c r="H191" s="1" t="s">
         <v>207</v>
       </c>
+      <c r="K191" s="1" t="s">
+        <v>491</v>
+      </c>
       <c r="L191" s="1" t="s">
-        <v>238</v>
+        <v>210</v>
       </c>
       <c r="M191" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="192" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B192" s="1" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>28</v>
@@ -8345,120 +8368,117 @@
         <v>21</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K192" s="1" t="s">
-        <v>496</v>
+        <v>207</v>
       </c>
       <c r="L192" s="1" t="s">
-        <v>213</v>
+        <v>238</v>
       </c>
       <c r="M192" s="1" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="193" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B193" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G193" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H193" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K193" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="L193" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="M193" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="194" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B194" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="C193" s="1" t="s">
+      <c r="C194" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="D193" s="1" t="s">
+      <c r="D194" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="E193" s="1" t="s">
+      <c r="E194" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="F193" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G193" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H193" s="1" t="s">
+      <c r="F194" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G194" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H194" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L193" s="1" t="s">
+      <c r="L194" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M193" s="1" t="s">
+      <c r="M194" s="1" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="194" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B194" s="9" t="s">
+    <row r="195" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B195" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="C194" s="9" t="s">
+      <c r="C195" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="D194" s="9" t="s">
+      <c r="D195" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="E194" s="9" t="s">
+      <c r="E195" s="9" t="s">
         <v>498</v>
       </c>
-      <c r="F194" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="G194" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H194" s="9" t="s">
+      <c r="F195" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G195" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H195" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="L194" s="9" t="s">
+      <c r="L195" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="M194" s="9" t="s">
+      <c r="M195" s="9" t="s">
         <v>252</v>
-      </c>
-    </row>
-    <row r="195" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B195" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="C195" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="E195" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="F195" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G195" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H195" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="K195" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="L195" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="M195" s="1" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="196" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B196" s="1" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>28</v>
@@ -8470,7 +8490,7 @@
         <v>207</v>
       </c>
       <c r="K196" s="1" t="s">
-        <v>324</v>
+        <v>499</v>
       </c>
       <c r="L196" s="1" t="s">
         <v>255</v>
@@ -8481,16 +8501,16 @@
     </row>
     <row r="197" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B197" s="1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>28</v>
@@ -8502,27 +8522,27 @@
         <v>207</v>
       </c>
       <c r="K197" s="1" t="s">
-        <v>491</v>
+        <v>324</v>
       </c>
       <c r="L197" s="1" t="s">
-        <v>210</v>
+        <v>255</v>
       </c>
       <c r="M197" s="1" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="198" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B198" s="1" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>28</v>
@@ -8533,25 +8553,28 @@
       <c r="H198" s="1" t="s">
         <v>207</v>
       </c>
+      <c r="K198" s="1" t="s">
+        <v>491</v>
+      </c>
       <c r="L198" s="1" t="s">
-        <v>277</v>
+        <v>210</v>
       </c>
       <c r="M198" s="1" t="s">
-        <v>278</v>
+        <v>235</v>
       </c>
     </row>
     <row r="199" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B199" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>28</v>
@@ -8563,24 +8586,24 @@
         <v>207</v>
       </c>
       <c r="L199" s="1" t="s">
-        <v>32</v>
+        <v>277</v>
       </c>
       <c r="M199" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="200" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B200" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>28</v>
@@ -8591,28 +8614,25 @@
       <c r="H200" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="K200" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="L200" s="1" t="s">
-        <v>284</v>
+        <v>32</v>
       </c>
       <c r="M200" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="201" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B201" s="1" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>28</v>
@@ -8623,25 +8643,28 @@
       <c r="H201" s="1" t="s">
         <v>207</v>
       </c>
+      <c r="K201" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L201" s="1" t="s">
-        <v>32</v>
+        <v>284</v>
       </c>
       <c r="M201" s="1" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
     </row>
     <row r="202" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B202" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>28</v>
@@ -8652,28 +8675,25 @@
       <c r="H202" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="K202" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="L202" s="1" t="s">
-        <v>251</v>
+        <v>32</v>
       </c>
       <c r="M202" s="1" t="s">
-        <v>252</v>
+        <v>294</v>
       </c>
     </row>
     <row r="203" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B203" s="1" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>359</v>
+        <v>507</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>28</v>
@@ -8682,30 +8702,30 @@
         <v>21</v>
       </c>
       <c r="H203" s="1" t="s">
-        <v>21</v>
+        <v>207</v>
       </c>
       <c r="K203" s="1" t="s">
-        <v>208</v>
+        <v>21</v>
       </c>
       <c r="L203" s="1" t="s">
-        <v>210</v>
+        <v>251</v>
       </c>
       <c r="M203" s="1" t="s">
-        <v>358</v>
+        <v>252</v>
       </c>
     </row>
     <row r="204" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B204" s="1" t="s">
-        <v>517</v>
+        <v>299</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>518</v>
+        <v>300</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>519</v>
+        <v>300</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>20</v>
+        <v>359</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>28</v>
@@ -8714,56 +8734,88 @@
         <v>21</v>
       </c>
       <c r="H204" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
+      </c>
+      <c r="K204" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="L204" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="M204" s="1" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="205" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B205" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G205" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H205" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="206" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B206" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="C205" s="1" t="s">
+      <c r="C206" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="D205" s="1" t="s">
+      <c r="D206" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="E205" s="1" t="s">
+      <c r="E206" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="F205" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G205" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H205" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="206" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="207" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B207" s="1" t="s">
+      <c r="F206" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G206" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H206" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="207" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="208" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B208" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C207" s="1" t="s">
+      <c r="C208" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D207" s="1" t="s">
+      <c r="D208" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E207" s="1" t="s">
+      <c r="E208" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="F207" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G207" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H207" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L207" s="1" t="s">
+      <c r="F208" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G208" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H208" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L208" s="1" t="s">
         <v>221</v>
       </c>
     </row>

--- a/Luban/Config/Datas/#BattleBuffConfig.xlsx
+++ b/Luban/Config/Datas/#BattleBuffConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8517EEAE-0CD4-4074-9C69-6F3076C9EAC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB9A5E8-2E70-41AB-9EBD-E844A9C07EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -95,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="533">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2067,10 +2067,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>BattleBuff74073</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>下回合刚炁自然恢复不会低于35</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2079,14 +2075,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>74073</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>下回合刚炁/玄气自然恢复不会低于35</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>下回合不会自然恢复炁</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3303,6 +3291,26 @@
   </si>
   <si>
     <t>无</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>740731</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleBuff740731</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>740732</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下回合玄气自然恢复不会低于35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleBuff740732</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3874,7 +3882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:N208"/>
+  <dimension ref="A1:N209"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.125" style="1" bestFit="1" customWidth="1"/>
@@ -3920,10 +3928,10 @@
         <v>16</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>330</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>33</v>
@@ -4005,10 +4013,10 @@
         <v>17</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>331</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>34</v>
@@ -4060,7 +4068,7 @@
         <v>123</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>22</v>
@@ -4072,13 +4080,13 @@
         <v>28</v>
       </c>
       <c r="I6" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="K6" s="1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>24</v>
@@ -4098,7 +4106,7 @@
         <v>124</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>22</v>
@@ -4127,7 +4135,7 @@
         <v>201</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>22</v>
@@ -4159,7 +4167,7 @@
         <v>202</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>22</v>
@@ -4191,7 +4199,7 @@
         <v>203</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>22</v>
@@ -4223,7 +4231,7 @@
         <v>204</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>22</v>
@@ -4235,7 +4243,7 @@
         <v>209</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>211</v>
@@ -4255,7 +4263,7 @@
         <v>205</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>22</v>
@@ -4267,7 +4275,7 @@
         <v>209</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>211</v>
@@ -4287,7 +4295,7 @@
         <v>125</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>22</v>
@@ -4299,7 +4307,7 @@
         <v>209</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>211</v>
@@ -4319,7 +4327,7 @@
         <v>126</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>22</v>
@@ -4331,7 +4339,7 @@
         <v>209</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>211</v>
@@ -4351,7 +4359,7 @@
         <v>206</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>22</v>
@@ -4363,7 +4371,7 @@
         <v>209</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>211</v>
@@ -4377,13 +4385,13 @@
         <v>10121</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>127</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>22</v>
@@ -4395,7 +4403,7 @@
         <v>22</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="N16" s="1" t="s">
         <v>22</v>
@@ -4412,7 +4420,7 @@
         <v>128</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>22</v>
@@ -4424,7 +4432,7 @@
         <v>22</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="N17" s="1" t="s">
         <v>22</v>
@@ -4438,10 +4446,10 @@
         <v>48</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>22</v>
@@ -4453,7 +4461,7 @@
         <v>209</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="L18" s="1" t="s">
         <v>210</v>
@@ -4467,13 +4475,13 @@
         <v>10151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>22</v>
@@ -4499,7 +4507,7 @@
         <v>10161</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>119</v>
@@ -4549,10 +4557,10 @@
         <v>21</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="N21" s="1" t="s">
         <v>22</v>
@@ -4566,10 +4574,10 @@
         <v>49</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>22</v>
@@ -4584,7 +4592,7 @@
         <v>208</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="N22" s="1" t="s">
         <v>22</v>
@@ -4613,10 +4621,10 @@
         <v>22</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="L23" s="1" t="s">
         <v>210</v>
@@ -4636,7 +4644,7 @@
         <v>122</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>22</v>
@@ -4648,7 +4656,7 @@
         <v>22</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="L24" s="1" t="s">
         <v>210</v>
@@ -4665,10 +4673,10 @@
         <v>52</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>22</v>
@@ -4680,7 +4688,7 @@
         <v>28</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="L25" s="1" t="s">
         <v>32</v>
@@ -4697,10 +4705,10 @@
         <v>53</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="F26" s="17" t="s">
         <v>22</v>
@@ -4712,7 +4720,7 @@
         <v>207</v>
       </c>
       <c r="K26" s="17" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="N26" s="17" t="s">
         <v>22</v>
@@ -4730,7 +4738,7 @@
         <v>129</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>21</v>
@@ -4763,7 +4771,7 @@
         <v>130</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>21</v>
@@ -4778,7 +4786,7 @@
         <v>11</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>29</v>
@@ -4798,13 +4806,13 @@
         <v>287</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>21</v>
@@ -4839,7 +4847,7 @@
         <v>20</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>21</v>
@@ -4874,7 +4882,7 @@
         <v>20</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>21</v>
@@ -4909,7 +4917,7 @@
         <v>20</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>21</v>
@@ -4944,7 +4952,7 @@
         <v>20</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G34" s="16" t="s">
         <v>21</v>
@@ -4972,10 +4980,10 @@
         <v>266</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>28</v>
@@ -4986,7 +4994,7 @@
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
       <c r="K35" s="1" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L35" s="1" t="s">
         <v>214</v>
@@ -5003,13 +5011,13 @@
         <v>58</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>28</v>
@@ -5037,13 +5045,13 @@
         <v>59</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>28</v>
@@ -5071,13 +5079,13 @@
         <v>60</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>28</v>
@@ -5088,7 +5096,7 @@
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
       <c r="K38" s="1" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="L38" s="1" t="s">
         <v>211</v>
@@ -5105,13 +5113,13 @@
         <v>61</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>28</v>
@@ -5122,7 +5130,7 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="1" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>211</v>
@@ -5139,13 +5147,13 @@
         <v>62</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>28</v>
@@ -5156,7 +5164,7 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="1" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="L40" s="1" t="s">
         <v>211</v>
@@ -5173,13 +5181,13 @@
         <v>63</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>28</v>
@@ -5190,7 +5198,7 @@
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
       <c r="K41" s="1" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="L41" s="1" t="s">
         <v>211</v>
@@ -5210,10 +5218,10 @@
         <v>135</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>28</v>
@@ -5224,7 +5232,7 @@
       <c r="I42" s="3"/>
       <c r="J42" s="3"/>
       <c r="K42" s="1" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="L42" s="1" t="s">
         <v>32</v>
@@ -5244,10 +5252,10 @@
         <v>136</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="F43" s="17" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G43" s="17" t="s">
         <v>28</v>
@@ -5275,10 +5283,10 @@
         <v>140</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>28</v>
@@ -5293,7 +5301,7 @@
         <v>0</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="L44" s="1" t="s">
         <v>24</v>
@@ -5313,10 +5321,10 @@
         <v>141</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>21</v>
@@ -5344,10 +5352,10 @@
         <v>142</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>21</v>
@@ -5375,10 +5383,10 @@
         <v>143</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>21</v>
@@ -5406,10 +5414,10 @@
         <v>144</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>21</v>
@@ -5434,13 +5442,13 @@
         <v>70</v>
       </c>
       <c r="D49" s="23" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F49" s="17" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G49" s="17" t="s">
         <v>28</v>
@@ -5465,10 +5473,10 @@
         <v>145</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="F50" s="17" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G50" s="17" t="s">
         <v>28</v>
@@ -5492,13 +5500,13 @@
         <v>72</v>
       </c>
       <c r="D51" s="23" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F51" s="17" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G51" s="17" t="s">
         <v>21</v>
@@ -5509,7 +5517,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="19"/>
       <c r="K51" s="17" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="L51" s="17" t="s">
         <v>32</v>
@@ -5523,16 +5531,16 @@
         <v>20251</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D52" s="23" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="F52" s="17" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G52" s="17" t="s">
         <v>21</v>
@@ -5543,7 +5551,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="19"/>
       <c r="K52" s="17" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="L52" s="17" t="s">
         <v>32</v>
@@ -5557,16 +5565,16 @@
         <v>20261</v>
       </c>
       <c r="C53" s="19" t="s">
+        <v>424</v>
+      </c>
+      <c r="D53" s="23" t="s">
         <v>427</v>
       </c>
-      <c r="D53" s="23" t="s">
-        <v>430</v>
-      </c>
       <c r="E53" s="17" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="F53" s="17" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G53" s="17" t="s">
         <v>21</v>
@@ -5577,7 +5585,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="19"/>
       <c r="K53" s="17" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="L53" s="17" t="s">
         <v>32</v>
@@ -5591,16 +5599,16 @@
         <v>20271</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D54" s="23" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="F54" s="17" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G54" s="17" t="s">
         <v>21</v>
@@ -5611,7 +5619,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="19"/>
       <c r="K54" s="17" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="L54" s="17" t="s">
         <v>32</v>
@@ -5625,7 +5633,7 @@
         <v>20281</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>137</v>
@@ -5634,7 +5642,7 @@
         <v>20</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>21</v>
@@ -5659,13 +5667,13 @@
         <v>73</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>21</v>
@@ -5693,13 +5701,13 @@
         <v>261</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>28</v>
@@ -5727,13 +5735,13 @@
         <v>257</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>28</v>
@@ -5764,10 +5772,10 @@
         <v>138</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>28</v>
@@ -5795,10 +5803,10 @@
         <v>139</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>21</v>
@@ -5809,7 +5817,7 @@
       <c r="I60" s="3"/>
       <c r="J60" s="3"/>
       <c r="K60" s="1" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="L60" s="1" t="s">
         <v>32</v>
@@ -5826,13 +5834,13 @@
         <v>241</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>28</v>
@@ -5854,13 +5862,13 @@
         <v>76</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>28</v>
@@ -5885,16 +5893,16 @@
         <v>20361</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>28</v>
@@ -5905,7 +5913,7 @@
       <c r="I63" s="3"/>
       <c r="J63" s="3"/>
       <c r="K63" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="64" spans="2:14" s="9" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -5917,10 +5925,10 @@
         <v>77</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>28</v>
@@ -5932,7 +5940,7 @@
         <v>29</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="N65" s="1" t="s">
         <v>22</v>
@@ -5949,7 +5957,7 @@
         <v>146</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>28</v>
@@ -5961,7 +5969,7 @@
         <v>1</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="L66" s="1" t="s">
         <v>210</v>
@@ -5978,7 +5986,7 @@
         <v>240</v>
       </c>
       <c r="D67" s="18" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E67" s="17" t="s">
         <v>20</v>
@@ -5993,10 +6001,10 @@
         <v>1</v>
       </c>
       <c r="I67" s="17" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="J67" s="17" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="N67" s="17" t="s">
         <v>22</v>
@@ -6013,7 +6021,7 @@
         <v>154</v>
       </c>
       <c r="E68" s="17" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="F68" s="17" t="s">
         <v>28</v>
@@ -6025,7 +6033,7 @@
         <v>1</v>
       </c>
       <c r="K68" s="17" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="N68" s="17" t="s">
         <v>22</v>
@@ -6042,7 +6050,7 @@
         <v>155</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>28</v>
@@ -6054,7 +6062,7 @@
         <v>29</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="N69" s="1" t="s">
         <v>22</v>
@@ -6065,13 +6073,13 @@
         <v>30071</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="D70" s="23" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="E70" s="17" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F70" s="17" t="s">
         <v>28</v>
@@ -6094,13 +6102,13 @@
         <v>30081</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>28</v>
@@ -6112,7 +6120,7 @@
         <v>1</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="N71" s="1" t="s">
         <v>22</v>
@@ -6129,7 +6137,7 @@
         <v>156</v>
       </c>
       <c r="E72" s="17" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F72" s="17" t="s">
         <v>28</v>
@@ -6155,7 +6163,7 @@
         <v>157</v>
       </c>
       <c r="E73" s="17" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="F73" s="17" t="s">
         <v>28</v>
@@ -6167,7 +6175,7 @@
         <v>29</v>
       </c>
       <c r="K73" s="17" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="N73" s="17" t="s">
         <v>22</v>
@@ -6184,7 +6192,7 @@
         <v>158</v>
       </c>
       <c r="E74" s="17" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="F74" s="17" t="s">
         <v>28</v>
@@ -6210,7 +6218,7 @@
         <v>159</v>
       </c>
       <c r="E75" s="17" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="F75" s="17" t="s">
         <v>28</v>
@@ -6236,7 +6244,7 @@
         <v>160</v>
       </c>
       <c r="E76" s="17" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="F76" s="17" t="s">
         <v>28</v>
@@ -6262,7 +6270,7 @@
         <v>161</v>
       </c>
       <c r="E77" s="17" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F77" s="17" t="s">
         <v>28</v>
@@ -6288,7 +6296,7 @@
         <v>162</v>
       </c>
       <c r="E78" s="17" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="F78" s="17" t="s">
         <v>28</v>
@@ -6314,7 +6322,7 @@
         <v>163</v>
       </c>
       <c r="E79" s="17" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F79" s="17" t="s">
         <v>28</v>
@@ -6340,7 +6348,7 @@
         <v>164</v>
       </c>
       <c r="E80" s="17" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F80" s="17" t="s">
         <v>28</v>
@@ -6366,7 +6374,7 @@
         <v>165</v>
       </c>
       <c r="E81" s="17" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="F81" s="17" t="s">
         <v>28</v>
@@ -6392,7 +6400,7 @@
         <v>166</v>
       </c>
       <c r="E82" s="17" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="F82" s="17" t="s">
         <v>28</v>
@@ -6418,7 +6426,7 @@
         <v>167</v>
       </c>
       <c r="E83" s="17" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="F83" s="17" t="s">
         <v>28</v>
@@ -6444,7 +6452,7 @@
         <v>168</v>
       </c>
       <c r="E84" s="17" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="F84" s="17" t="s">
         <v>28</v>
@@ -6470,7 +6478,7 @@
         <v>169</v>
       </c>
       <c r="E85" s="17" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="F85" s="17" t="s">
         <v>28</v>
@@ -6496,7 +6504,7 @@
         <v>170</v>
       </c>
       <c r="E86" s="17" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="F86" s="17" t="s">
         <v>28</v>
@@ -6522,7 +6530,7 @@
         <v>171</v>
       </c>
       <c r="E87" s="17" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="F87" s="17" t="s">
         <v>28</v>
@@ -6548,7 +6556,7 @@
         <v>172</v>
       </c>
       <c r="E88" s="17" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="F88" s="17" t="s">
         <v>28</v>
@@ -6574,7 +6582,7 @@
         <v>173</v>
       </c>
       <c r="E89" s="17" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="F89" s="17" t="s">
         <v>28</v>
@@ -6594,13 +6602,13 @@
         <v>30271</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>28</v>
@@ -6612,7 +6620,7 @@
         <v>1</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="N90" s="1" t="s">
         <v>22</v>
@@ -6629,7 +6637,7 @@
         <v>147</v>
       </c>
       <c r="E91" s="17" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="F91" s="17" t="s">
         <v>28</v>
@@ -6638,7 +6646,7 @@
         <v>28</v>
       </c>
       <c r="K91" s="17" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="N91" s="17" t="s">
         <v>22</v>
@@ -6681,7 +6689,7 @@
         <v>149</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>28</v>
@@ -6690,7 +6698,7 @@
         <v>28</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="N93" s="1" t="s">
         <v>22</v>
@@ -6722,10 +6730,10 @@
         <v>30321</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>20</v>
@@ -6740,10 +6748,10 @@
         <v>1</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="N95" s="1" t="s">
         <v>22</v>
@@ -6751,16 +6759,16 @@
     </row>
     <row r="96" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B96" s="1" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>28</v>
@@ -6775,7 +6783,7 @@
         <v>210</v>
       </c>
       <c r="M96" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="N96" s="1" t="s">
         <v>22</v>
@@ -6806,16 +6814,16 @@
     </row>
     <row r="98" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B98" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="G98" s="1" t="s">
         <v>21</v>
@@ -6824,13 +6832,13 @@
         <v>207</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="L98" s="1" t="s">
         <v>210</v>
       </c>
       <c r="M98" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="99" spans="2:14" x14ac:dyDescent="0.2">
@@ -6844,7 +6852,7 @@
         <v>151</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>28</v>
@@ -6867,10 +6875,10 @@
         <v>104</v>
       </c>
       <c r="D100" s="18" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E100" s="17" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="F100" s="17" t="s">
         <v>28</v>
@@ -6882,7 +6890,7 @@
         <v>8</v>
       </c>
       <c r="K100" s="17" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="N100" s="17" t="s">
         <v>22</v>
@@ -6896,10 +6904,10 @@
         <v>105</v>
       </c>
       <c r="D101" s="18" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E101" s="17" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="F101" s="17" t="s">
         <v>28</v>
@@ -6911,7 +6919,7 @@
         <v>8</v>
       </c>
       <c r="K101" s="17" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="N101" s="17" t="s">
         <v>22</v>
@@ -6925,10 +6933,10 @@
         <v>106</v>
       </c>
       <c r="D102" s="18" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E102" s="17" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="F102" s="17" t="s">
         <v>28</v>
@@ -6940,7 +6948,7 @@
         <v>8</v>
       </c>
       <c r="K102" s="17" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="N102" s="17" t="s">
         <v>22</v>
@@ -6957,7 +6965,7 @@
         <v>152</v>
       </c>
       <c r="E103" s="17" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F103" s="17" t="s">
         <v>28</v>
@@ -6966,7 +6974,7 @@
         <v>28</v>
       </c>
       <c r="K103" s="17" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="N103" s="17" t="s">
         <v>22</v>
@@ -6983,7 +6991,7 @@
         <v>153</v>
       </c>
       <c r="E104" s="17" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F104" s="17" t="s">
         <v>28</v>
@@ -7068,7 +7076,7 @@
         <v>21</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="109" spans="2:14" x14ac:dyDescent="0.2">
@@ -7091,7 +7099,7 @@
         <v>21</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="110" spans="2:14" x14ac:dyDescent="0.2">
@@ -7114,7 +7122,7 @@
         <v>21</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="111" spans="2:14" x14ac:dyDescent="0.2">
@@ -7137,7 +7145,7 @@
         <v>21</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="112" spans="2:14" x14ac:dyDescent="0.2">
@@ -7183,7 +7191,7 @@
         <v>28</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="114" spans="2:11" x14ac:dyDescent="0.2">
@@ -7206,7 +7214,7 @@
         <v>28</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="115" spans="2:11" x14ac:dyDescent="0.2">
@@ -7229,7 +7237,7 @@
         <v>28</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="116" spans="2:11" x14ac:dyDescent="0.2">
@@ -7252,7 +7260,7 @@
         <v>28</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="117" spans="2:11" x14ac:dyDescent="0.2">
@@ -7321,7 +7329,7 @@
         <v>28</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="120" spans="2:11" x14ac:dyDescent="0.2">
@@ -7344,7 +7352,7 @@
         <v>28</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="121" spans="2:11" x14ac:dyDescent="0.2">
@@ -7367,7 +7375,7 @@
         <v>28</v>
       </c>
       <c r="K121" s="1" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="122" spans="2:11" x14ac:dyDescent="0.2">
@@ -7390,7 +7398,7 @@
         <v>28</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="123" spans="2:11" x14ac:dyDescent="0.2">
@@ -7413,7 +7421,7 @@
         <v>28</v>
       </c>
       <c r="K123" s="1" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="124" spans="2:11" x14ac:dyDescent="0.2">
@@ -7436,7 +7444,7 @@
         <v>28</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="125" spans="2:11" x14ac:dyDescent="0.2">
@@ -7459,7 +7467,7 @@
         <v>28</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="126" spans="2:11" x14ac:dyDescent="0.2">
@@ -7482,7 +7490,7 @@
         <v>28</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="127" spans="2:11" x14ac:dyDescent="0.2">
@@ -7505,7 +7513,7 @@
         <v>28</v>
       </c>
       <c r="K127" s="1" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="128" spans="2:11" x14ac:dyDescent="0.2">
@@ -7528,7 +7536,7 @@
         <v>28</v>
       </c>
       <c r="K128" s="1" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="129" spans="2:11" x14ac:dyDescent="0.2">
@@ -7551,7 +7559,7 @@
         <v>28</v>
       </c>
       <c r="K129" s="1" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="130" spans="2:11" x14ac:dyDescent="0.2">
@@ -7577,7 +7585,7 @@
         <v>3</v>
       </c>
       <c r="K130" s="1" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="131" spans="2:11" x14ac:dyDescent="0.2">
@@ -7603,7 +7611,7 @@
         <v>3</v>
       </c>
       <c r="K131" s="1" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="132" spans="2:11" x14ac:dyDescent="0.2">
@@ -7611,7 +7619,7 @@
         <v>40261</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="D132" s="3" t="s">
         <v>195</v>
@@ -7629,7 +7637,7 @@
         <v>99</v>
       </c>
       <c r="K132" s="1" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="133" spans="2:11" x14ac:dyDescent="0.2">
@@ -7637,7 +7645,7 @@
         <v>40271</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="D133" s="3" t="s">
         <v>190</v>
@@ -7655,7 +7663,7 @@
         <v>99</v>
       </c>
       <c r="K133" s="1" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="134" spans="2:11" x14ac:dyDescent="0.2">
@@ -7663,7 +7671,7 @@
         <v>40281</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="D134" s="3" t="s">
         <v>191</v>
@@ -7681,7 +7689,7 @@
         <v>99</v>
       </c>
       <c r="K134" s="1" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="135" spans="2:11" x14ac:dyDescent="0.2">
@@ -7689,7 +7697,7 @@
         <v>40291</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="D135" s="3" t="s">
         <v>192</v>
@@ -7707,7 +7715,7 @@
         <v>99</v>
       </c>
       <c r="K135" s="1" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="136" spans="2:11" x14ac:dyDescent="0.2">
@@ -7715,7 +7723,7 @@
         <v>40301</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D136" s="3" t="s">
         <v>193</v>
@@ -7733,7 +7741,7 @@
         <v>99</v>
       </c>
       <c r="K136" s="1" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="137" spans="2:11" x14ac:dyDescent="0.2">
@@ -7741,7 +7749,7 @@
         <v>40311</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D137" s="3" t="s">
         <v>196</v>
@@ -7759,7 +7767,7 @@
         <v>99</v>
       </c>
       <c r="K137" s="1" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="138" spans="2:11" x14ac:dyDescent="0.2">
@@ -7981,7 +7989,7 @@
         <v>24</v>
       </c>
       <c r="M176" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="177" spans="1:13" x14ac:dyDescent="0.2">
@@ -8010,21 +8018,21 @@
         <v>210</v>
       </c>
       <c r="M177" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="178" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B178" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>28</v>
@@ -8042,21 +8050,21 @@
         <v>24</v>
       </c>
       <c r="M178" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="179" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B179" s="1" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>28</v>
@@ -8068,24 +8076,24 @@
         <v>207</v>
       </c>
       <c r="K179" s="1" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="M179" s="1" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="180" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B180" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C180" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="E180" s="1" t="s">
         <v>306</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="E180" s="1" t="s">
-        <v>309</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>28</v>
@@ -8097,27 +8105,27 @@
         <v>207</v>
       </c>
       <c r="K180" s="1" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="L180" s="1" t="s">
         <v>210</v>
       </c>
       <c r="M180" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="181" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B181" s="1" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>28</v>
@@ -8132,21 +8140,21 @@
         <v>210</v>
       </c>
       <c r="M181" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="182" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B182" s="1" t="s">
-        <v>295</v>
+        <v>528</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>292</v>
+        <v>529</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>28</v>
@@ -8158,58 +8166,64 @@
         <v>207</v>
       </c>
       <c r="K182" s="1" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="L182" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M182" s="1" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="184" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A184" s="9" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="183" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B183" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G183" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H183" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="K183" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="L183" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M183" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="185" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A185" s="9" t="s">
         <v>215</v>
-      </c>
-    </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B185" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="C185" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E185" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="F185" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G185" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H185" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L185" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="186" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B186" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>36</v>
+        <v>521</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>28</v>
@@ -8220,25 +8234,22 @@
       <c r="H186" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K186" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M186" s="1" t="s">
-        <v>230</v>
+      <c r="L186" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="187" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B187" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>216</v>
+        <v>30</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>216</v>
+        <v>31</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>28</v>
@@ -8249,22 +8260,25 @@
       <c r="H187" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L187" s="1" t="s">
-        <v>24</v>
+      <c r="K187" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M187" s="1" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="188" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B188" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>218</v>
+        <v>20</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>28</v>
@@ -8275,59 +8289,56 @@
       <c r="H188" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K188" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M188" s="1" t="s">
+      <c r="L188" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="189" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B189" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G189" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H189" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K189" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M189" s="1" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="189" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A189" s="9" t="s">
+    <row r="190" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A190" s="9" t="s">
         <v>222</v>
-      </c>
-    </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B190" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C190" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="E190" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="F190" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G190" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H190" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="L190" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="M190" s="1" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="191" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B191" s="1" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>28</v>
@@ -8338,28 +8349,25 @@
       <c r="H191" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="K191" s="1" t="s">
+      <c r="L191" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="M191" s="1" t="s">
         <v>491</v>
-      </c>
-      <c r="L191" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="M191" s="1" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="192" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B192" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>28</v>
@@ -8370,25 +8378,28 @@
       <c r="H192" s="1" t="s">
         <v>207</v>
       </c>
+      <c r="K192" s="1" t="s">
+        <v>488</v>
+      </c>
       <c r="L192" s="1" t="s">
-        <v>238</v>
+        <v>210</v>
       </c>
       <c r="M192" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="193" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B193" s="1" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>28</v>
@@ -8397,120 +8408,117 @@
         <v>21</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K193" s="1" t="s">
-        <v>496</v>
+        <v>207</v>
       </c>
       <c r="L193" s="1" t="s">
-        <v>213</v>
+        <v>238</v>
       </c>
       <c r="M193" s="1" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="194" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B194" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E194" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="F194" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G194" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H194" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K194" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="L194" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="M194" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="195" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B195" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="C194" s="1" t="s">
+      <c r="C195" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="D194" s="1" t="s">
+      <c r="D195" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="E194" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="F194" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G194" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H194" s="1" t="s">
+      <c r="E195" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G195" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H195" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L194" s="1" t="s">
+      <c r="L195" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M194" s="1" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="195" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B195" s="9" t="s">
+      <c r="M195" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="196" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B196" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="C195" s="9" t="s">
+      <c r="C196" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="D195" s="9" t="s">
+      <c r="D196" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="E195" s="9" t="s">
-        <v>498</v>
-      </c>
-      <c r="F195" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="G195" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H195" s="9" t="s">
+      <c r="E196" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="F196" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G196" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H196" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="L195" s="9" t="s">
+      <c r="L196" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="M195" s="9" t="s">
+      <c r="M196" s="9" t="s">
         <v>252</v>
-      </c>
-    </row>
-    <row r="196" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B196" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="C196" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="D196" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="E196" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="F196" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G196" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H196" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="K196" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="L196" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="M196" s="1" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="197" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B197" s="1" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>28</v>
@@ -8522,7 +8530,7 @@
         <v>207</v>
       </c>
       <c r="K197" s="1" t="s">
-        <v>324</v>
+        <v>496</v>
       </c>
       <c r="L197" s="1" t="s">
         <v>255</v>
@@ -8533,16 +8541,16 @@
     </row>
     <row r="198" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B198" s="1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>28</v>
@@ -8554,27 +8562,27 @@
         <v>207</v>
       </c>
       <c r="K198" s="1" t="s">
-        <v>491</v>
+        <v>321</v>
       </c>
       <c r="L198" s="1" t="s">
-        <v>210</v>
+        <v>255</v>
       </c>
       <c r="M198" s="1" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="199" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B199" s="1" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>28</v>
@@ -8585,25 +8593,28 @@
       <c r="H199" s="1" t="s">
         <v>207</v>
       </c>
+      <c r="K199" s="1" t="s">
+        <v>488</v>
+      </c>
       <c r="L199" s="1" t="s">
-        <v>277</v>
+        <v>210</v>
       </c>
       <c r="M199" s="1" t="s">
-        <v>278</v>
+        <v>235</v>
       </c>
     </row>
     <row r="200" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B200" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>28</v>
@@ -8615,24 +8626,24 @@
         <v>207</v>
       </c>
       <c r="L200" s="1" t="s">
-        <v>32</v>
+        <v>277</v>
       </c>
       <c r="M200" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="201" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B201" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>28</v>
@@ -8643,28 +8654,25 @@
       <c r="H201" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="K201" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="L201" s="1" t="s">
-        <v>284</v>
+        <v>32</v>
       </c>
       <c r="M201" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="202" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B202" s="1" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>28</v>
@@ -8675,25 +8683,28 @@
       <c r="H202" s="1" t="s">
         <v>207</v>
       </c>
+      <c r="K202" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L202" s="1" t="s">
-        <v>32</v>
+        <v>284</v>
       </c>
       <c r="M202" s="1" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
     </row>
     <row r="203" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B203" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>28</v>
@@ -8704,28 +8715,25 @@
       <c r="H203" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="K203" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="L203" s="1" t="s">
-        <v>251</v>
+        <v>32</v>
       </c>
       <c r="M203" s="1" t="s">
-        <v>252</v>
+        <v>293</v>
       </c>
     </row>
     <row r="204" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B204" s="1" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>359</v>
+        <v>504</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>28</v>
@@ -8734,30 +8742,30 @@
         <v>21</v>
       </c>
       <c r="H204" s="1" t="s">
-        <v>21</v>
+        <v>207</v>
       </c>
       <c r="K204" s="1" t="s">
-        <v>208</v>
+        <v>21</v>
       </c>
       <c r="L204" s="1" t="s">
-        <v>210</v>
+        <v>251</v>
       </c>
       <c r="M204" s="1" t="s">
-        <v>358</v>
+        <v>252</v>
       </c>
     </row>
     <row r="205" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B205" s="1" t="s">
-        <v>517</v>
+        <v>296</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>518</v>
+        <v>297</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>519</v>
+        <v>297</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>20</v>
+        <v>356</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>28</v>
@@ -8766,56 +8774,88 @@
         <v>21</v>
       </c>
       <c r="H205" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
+      </c>
+      <c r="K205" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="L205" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="M205" s="1" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="206" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B206" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F206" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G206" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H206" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="207" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B207" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="E207" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="C206" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="D206" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="E206" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="F206" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G206" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H206" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="207" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="208" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B208" s="1" t="s">
+      <c r="F207" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G207" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H207" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="208" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="209" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B209" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C208" s="1" t="s">
+      <c r="C209" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D208" s="1" t="s">
+      <c r="D209" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E208" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="F208" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G208" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H208" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L208" s="1" t="s">
+      <c r="E209" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="F209" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G209" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H209" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L209" s="1" t="s">
         <v>221</v>
       </c>
     </row>

--- a/Luban/Config/Datas/#BattleBuffConfig.xlsx
+++ b/Luban/Config/Datas/#BattleBuffConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E646B2-D46C-4BAC-A828-D663CAF6DBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C622A8D7-CBBA-4374-8B0C-0138B233E6E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -95,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="546">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3320,6 +3320,54 @@
   </si>
   <si>
     <t>BattleBuff72008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下个回合玄炁的自然恢复增加3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下个回合刚炁的自然恢复增加3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>75011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>75012</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleBuff75011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleBuff75012</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>75021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>75022</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下个回合玄炁的自然恢复增加5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下个回合刚炁的自然恢复增加5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleBuff75021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleBuff75022</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3888,7 +3936,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:N209"/>
+  <dimension ref="A1:N212"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.125" style="1" bestFit="1" customWidth="1"/>
@@ -8213,104 +8261,151 @@
         <v>281</v>
       </c>
     </row>
-    <row r="185" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A185" s="8" t="s">
-        <v>204</v>
+    <row r="184" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B184" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G184" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H184" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="K184" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L184" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M184" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="185" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B185" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G185" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H185" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="K185" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L185" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M185" s="1" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="186" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B186" s="1" t="s">
-        <v>213</v>
+        <v>540</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>27</v>
+        <v>542</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>26</v>
+        <v>542</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>509</v>
+        <v>544</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="H186" s="1" t="s">
-        <v>29</v>
+        <v>196</v>
+      </c>
+      <c r="K186" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="L186" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
+      </c>
+      <c r="M186" s="1" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="187" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B187" s="1" t="s">
-        <v>214</v>
+        <v>541</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>30</v>
+        <v>543</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>31</v>
+        <v>543</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>36</v>
+        <v>545</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="H187" s="1" t="s">
-        <v>29</v>
+        <v>196</v>
       </c>
       <c r="K187" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
+      </c>
+      <c r="L187" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="M187" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B188" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="E188" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F188" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G188" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H188" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L188" s="1" t="s">
-        <v>24</v>
+        <v>281</v>
+      </c>
+    </row>
+    <row r="188" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A188" s="8" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="189" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B189" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>206</v>
+        <v>27</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>206</v>
+        <v>26</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>207</v>
+        <v>509</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>28</v>
@@ -8321,152 +8416,140 @@
       <c r="H189" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K189" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M189" s="1" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="190" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A190" s="8" t="s">
-        <v>211</v>
+      <c r="L189" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="190" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B190" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G190" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H190" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K190" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M190" s="1" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="191" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B191" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>474</v>
+        <v>20</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H191" s="1" t="s">
-        <v>196</v>
+        <v>29</v>
       </c>
       <c r="L191" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="M191" s="1" t="s">
-        <v>479</v>
+        <v>24</v>
       </c>
     </row>
     <row r="192" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B192" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G192" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H192" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K192" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M192" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="193" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A193" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="194" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B194" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E194" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="F194" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G194" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H194" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="L194" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="M194" s="1" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="195" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B195" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C192" s="1" t="s">
+      <c r="C195" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="D192" s="1" t="s">
+      <c r="D195" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="E192" s="1" t="s">
+      <c r="E195" s="1" t="s">
         <v>475</v>
-      </c>
-      <c r="F192" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G192" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H192" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="K192" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="L192" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="M192" s="1" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="193" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B193" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="D193" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="E193" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="F193" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G193" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H193" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="L193" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="M193" s="1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="194" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B194" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="D194" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="E194" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="F194" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G194" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H194" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K194" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="L194" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="M194" s="1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="195" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B195" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="C195" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="E195" s="1" t="s">
-        <v>482</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>28</v>
@@ -8477,54 +8560,57 @@
       <c r="H195" s="1" t="s">
         <v>196</v>
       </c>
+      <c r="K195" s="1" t="s">
+        <v>476</v>
+      </c>
       <c r="L195" s="1" t="s">
-        <v>32</v>
+        <v>199</v>
       </c>
       <c r="M195" s="1" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="196" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B196" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="C196" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="D196" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="E196" s="8" t="s">
-        <v>483</v>
-      </c>
-      <c r="F196" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G196" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H196" s="8" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="196" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B196" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="F196" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G196" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H196" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="L196" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="M196" s="8" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="197" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="L196" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="M196" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="197" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B197" s="1" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>28</v>
@@ -8533,30 +8619,30 @@
         <v>21</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>196</v>
+        <v>22</v>
       </c>
       <c r="K197" s="1" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="L197" s="1" t="s">
-        <v>244</v>
+        <v>202</v>
       </c>
       <c r="M197" s="1" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="198" spans="2:13" x14ac:dyDescent="0.2">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="198" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B198" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>28</v>
@@ -8567,60 +8653,54 @@
       <c r="H198" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="K198" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="L198" s="1" t="s">
-        <v>244</v>
+        <v>32</v>
       </c>
       <c r="M198" s="1" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="199" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B199" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="C199" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="D199" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="E199" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="F199" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G199" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H199" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="199" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B199" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="C199" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="D199" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="E199" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="F199" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G199" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H199" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="K199" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="L199" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="M199" s="1" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="200" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="L199" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="M199" s="8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="200" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B200" s="1" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>264</v>
+        <v>243</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>264</v>
+        <v>243</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>28</v>
@@ -8631,25 +8711,28 @@
       <c r="H200" s="1" t="s">
         <v>196</v>
       </c>
+      <c r="K200" s="1" t="s">
+        <v>484</v>
+      </c>
       <c r="L200" s="1" t="s">
-        <v>265</v>
+        <v>244</v>
       </c>
       <c r="M200" s="1" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="201" spans="2:13" x14ac:dyDescent="0.2">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="201" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B201" s="1" t="s">
-        <v>267</v>
+        <v>248</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>28</v>
@@ -8660,25 +8743,28 @@
       <c r="H201" s="1" t="s">
         <v>196</v>
       </c>
+      <c r="K201" s="1" t="s">
+        <v>309</v>
+      </c>
       <c r="L201" s="1" t="s">
-        <v>32</v>
+        <v>244</v>
       </c>
       <c r="M201" s="1" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="202" spans="2:13" x14ac:dyDescent="0.2">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="202" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B202" s="1" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>28</v>
@@ -8690,27 +8776,27 @@
         <v>196</v>
       </c>
       <c r="K202" s="1" t="s">
-        <v>22</v>
+        <v>476</v>
       </c>
       <c r="L202" s="1" t="s">
-        <v>272</v>
+        <v>199</v>
       </c>
       <c r="M202" s="1" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="203" spans="2:13" x14ac:dyDescent="0.2">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="203" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B203" s="1" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>28</v>
@@ -8722,24 +8808,24 @@
         <v>196</v>
       </c>
       <c r="L203" s="1" t="s">
-        <v>32</v>
+        <v>265</v>
       </c>
       <c r="M203" s="1" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="204" spans="2:13" x14ac:dyDescent="0.2">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="204" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B204" s="1" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>28</v>
@@ -8750,118 +8836,208 @@
       <c r="H204" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="K204" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="L204" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M204" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="205" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B205" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G205" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H205" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="K205" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L205" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="M205" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="206" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B206" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="F206" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G206" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H206" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="L206" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M206" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="207" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B207" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="F207" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G207" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H207" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="K207" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L207" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="M204" s="1" t="s">
+      <c r="M207" s="1" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="205" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B205" s="1" t="s">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B208" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C205" s="1" t="s">
+      <c r="C208" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="D205" s="1" t="s">
+      <c r="D208" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E205" s="1" t="s">
+      <c r="E208" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="F205" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G205" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H205" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K205" s="1" t="s">
+      <c r="F208" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G208" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H208" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K208" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="L205" s="1" t="s">
+      <c r="L208" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="M205" s="1" t="s">
+      <c r="M208" s="1" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="206" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B206" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="C206" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="D206" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="E206" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F206" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G206" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H206" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="207" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B207" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="D207" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="E207" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="F207" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G207" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H207" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="208" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="209" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B209" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="D209" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F209" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G209" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H209" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="210" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B210" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="F210" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G210" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H210" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="211" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="212" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B212" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C209" s="1" t="s">
+      <c r="C212" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D209" s="1" t="s">
+      <c r="D212" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E209" s="1" t="s">
+      <c r="E212" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="F209" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G209" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H209" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L209" s="1" t="s">
+      <c r="F212" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G212" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H212" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L212" s="1" t="s">
         <v>210</v>
       </c>
     </row>
